--- a/execution-substrates/xlsx/rulebook.xlsx
+++ b/execution-substrates/xlsx/rulebook.xlsx
@@ -459,7 +459,7 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -506,7 +506,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>CountOfSteps</t>
+          <t>CountOfNonProposedSteps</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>onboarding</t>
+          <t>performance-review</t>
         </is>
       </c>
       <c r="B2" s="3">
@@ -527,36 +527,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Performance Review</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Employee Onboarding</t>
+          <t>Annual Performance Review</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>A step-by-step process to onboard new employees, including document collection, orientation, and training.</t>
+          <t>Structured workflow for conducting annual employee performance evaluations.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>WF-ONB-001</t>
+          <t>WF-PRV-007</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>submit-request</t>
+          <t>system-notification-sent, step-2, recwwXHLqxKPhj6Mt</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J2" s="3">
         <f>$I2 &gt; 1</f>
@@ -566,7 +566,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>invoice-approval</t>
+          <t>change-management</t>
         </is>
       </c>
       <c r="B3" s="3">
@@ -575,36 +575,36 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Invoice Approval</t>
+          <t>Change Management</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Invoice Approval Workflow</t>
+          <t>Change Management Workflow</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Automated workflow for reviewing, approving, and processing vendor invoices.</t>
+          <t>Structured process for requesting, evaluating, and implementing organizational changes.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>WF-INV-002</t>
+          <t>WF-CHM-015</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>manager-review</t>
+          <t>close-workflow, step1, asdf</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3" s="3">
         <f>$I3 &gt; 1</f>
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>content-publishing</t>
+          <t>asset-management</t>
         </is>
       </c>
       <c r="B4" s="3">
@@ -623,36 +623,36 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Content Publishing</t>
+          <t>Asset Management</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Content Publishing Process</t>
+          <t>Asset Management Process</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Workflow for drafting, reviewing, and publishing content to the company website.</t>
+          <t>Process for tracking, maintaining, and auditing company assets.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>WF-CNT-003</t>
+          <t>WF-ASM-012</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>automated-eligibility-check</t>
+          <t>assign-task-to-team, some-new-task</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" s="3">
         <f>$I4 &gt; 1</f>
@@ -662,7 +662,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>leave-request</t>
+          <t>incident-reporting</t>
         </is>
       </c>
       <c r="B5" s="3">
@@ -671,32 +671,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Leave Request</t>
+          <t>Incident Reporting</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Leave Request Workflow</t>
+          <t>Incident Reporting Process</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Process for employees to submit, review, and approve leave requests.</t>
+          <t>Steps for reporting, investigating, and resolving workplace incidents.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>WF-LRQ-004</t>
+          <t>WF-INC-014</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>finance-approval</t>
+          <t>generate-report</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
@@ -710,7 +710,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>it-support</t>
+          <t>customer-feedback</t>
         </is>
       </c>
       <c r="B6" s="3">
@@ -719,32 +719,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>IT Support</t>
+          <t>Customer Feedback</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>IT Support Ticketing</t>
+          <t>Customer Feedback Collection</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Workflow for submitting, triaging, and resolving IT support tickets.</t>
+          <t>Workflow for collecting, analyzing, and acting on customer feedback.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>WF-ITS-005</t>
+          <t>WF-CFB-009</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>document-verification</t>
+          <t>archive-request</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
@@ -758,7 +758,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>expense-reimbursement</t>
+          <t>project-kickoff</t>
         </is>
       </c>
       <c r="B7" s="3">
@@ -767,32 +767,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Expense Reimbursement</t>
+          <t>Project Kickoff</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Expense Reimbursement Process</t>
+          <t>Project Kickoff Process</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Steps for employees to submit expenses and receive reimbursements after approval.</t>
+          <t>Steps to initiate a new project, including team assignment and goal setting.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>WF-EXP-006</t>
+          <t>WF-PKO-010</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>quality-assurance-review</t>
+          <t>customer-feedback-collection</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
@@ -806,7 +806,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>performance-review</t>
+          <t>onboarding</t>
         </is>
       </c>
       <c r="B8" s="3">
@@ -815,32 +815,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Performance Review</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Annual Performance Review</t>
+          <t>Employee Onboarding</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Structured workflow for conducting annual employee performance evaluations.</t>
+          <t>A step-by-step process to onboard new employees, including document collection, orientation, and training.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>WF-PRV-007</t>
+          <t>WF-ONB-001</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>system-notification-sent</t>
+          <t>submit-request</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
@@ -854,7 +854,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>procurement</t>
+          <t>content-publishing</t>
         </is>
       </c>
       <c r="B9" s="3">
@@ -863,32 +863,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Content Publishing</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Procurement Workflow</t>
+          <t>Content Publishing Process</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Process for requesting, approving, and purchasing goods or services.</t>
+          <t>Workflow for drafting, reviewing, and publishing content to the company website.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>WF-PRC-008</t>
+          <t>WF-CNT-003</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>final-approval</t>
+          <t>automated-eligibility-check</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
@@ -902,7 +902,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>customer-feedback</t>
+          <t>expense-reimbursement</t>
         </is>
       </c>
       <c r="B10" s="3">
@@ -911,32 +911,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Customer Feedback</t>
+          <t>Expense Reimbursement</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Customer Feedback Collection</t>
+          <t>Expense Reimbursement Process</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Workflow for collecting, analyzing, and acting on customer feedback.</t>
+          <t>Steps for employees to submit expenses and receive reimbursements after approval.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>WF-CFB-009</t>
+          <t>WF-EXP-006</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>archive-request</t>
+          <t>quality-assurance-review</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
@@ -950,7 +950,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>project-kickoff</t>
+          <t>procurement</t>
         </is>
       </c>
       <c r="B11" s="3">
@@ -959,32 +959,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Project Kickoff</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Project Kickoff Process</t>
+          <t>Procurement Workflow</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Steps to initiate a new project, including team assignment and goal setting.</t>
+          <t>Process for requesting, approving, and purchasing goods or services.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>WF-PKO-010</t>
+          <t>WF-PRC-008</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>customer-feedback-collection</t>
+          <t>final-approval</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
@@ -998,7 +998,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>contract-review</t>
+          <t>invoice-approval</t>
         </is>
       </c>
       <c r="B12" s="3">
@@ -1007,32 +1007,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Contract Review</t>
+          <t>Invoice Approval</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Contract Review Workflow</t>
+          <t>Invoice Approval Workflow</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Workflow for legal and management review of contracts before signing.</t>
+          <t>Automated workflow for reviewing, approving, and processing vendor invoices.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>WF-CTR-011</t>
+          <t>WF-INV-002</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>legal-compliance-check</t>
+          <t>manager-review</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
@@ -1046,7 +1046,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>asset-management</t>
+          <t>contract-review</t>
         </is>
       </c>
       <c r="B13" s="3">
@@ -1055,36 +1055,36 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Asset Management</t>
+          <t>Contract Review</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Asset Management Process</t>
+          <t>Contract Review Workflow</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Process for tracking, maintaining, and auditing company assets.</t>
+          <t>Workflow for legal and management review of contracts before signing.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>WF-ASM-012</t>
+          <t>WF-CTR-011</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>assign-task-to-team, some-new-task</t>
+          <t>legal-compliance-check</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13" s="3">
         <f>$I13 &gt; 1</f>
@@ -1142,7 +1142,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>incident-reporting</t>
+          <t>it-support</t>
         </is>
       </c>
       <c r="B15" s="3">
@@ -1151,32 +1151,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Incident Reporting</t>
+          <t>IT Support</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Incident Reporting Process</t>
+          <t>IT Support Ticketing</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Steps for reporting, investigating, and resolving workplace incidents.</t>
+          <t>Workflow for submitting, triaging, and resolving IT support tickets.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>WF-INC-014</t>
+          <t>WF-ITS-005</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>generate-report</t>
+          <t>document-verification</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
@@ -1190,7 +1190,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>change-management</t>
+          <t>leave-request</t>
         </is>
       </c>
       <c r="B16" s="3">
@@ -1199,32 +1199,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Change Management</t>
+          <t>Leave Request</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Change Management Workflow</t>
+          <t>Leave Request Workflow</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Structured process for requesting, evaluating, and implementing organizational changes.</t>
+          <t>Process for employees to submit, review, and approve leave requests.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>WF-CHM-015</t>
+          <t>WF-LRQ-004</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>close-workflow</t>
+          <t>finance-approval</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
@@ -1246,7 +1246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1394,49 +1394,33 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>automated-eligibility-check</t>
+          <t>recwwXHLqxKPhj6Mt</t>
         </is>
       </c>
       <c r="B4" s="3">
         <f>SUBSTITUTE(LOWER($C4), " ", "-")</f>
         <v/>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Automated Eligibility Check</t>
-        </is>
-      </c>
+      <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>content-publishing</t>
+          <t>performance-review</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>viewer</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>it-security-gate</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>step-3</t>
-        </is>
-      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>finance-approval</t>
+          <t>automated-eligibility-check</t>
         </is>
       </c>
       <c r="B5" s="3">
@@ -1445,40 +1429,40 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Finance Approval</t>
+          <t>Automated Eligibility Check</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>leave-request</t>
+          <t>content-publishing</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>moderator</t>
+          <t>viewer</t>
         </is>
       </c>
       <c r="G5" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>finance-approval</t>
+          <t>it-security-gate</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>step-4</t>
+          <t>step-3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>document-verification</t>
+          <t>finance-approval</t>
         </is>
       </c>
       <c r="B6" s="3">
@@ -1487,40 +1471,40 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Document Verification</t>
+          <t>Finance Approval</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>it-support</t>
+          <t>leave-request</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>contributor</t>
+          <t>moderator</t>
         </is>
       </c>
       <c r="G6" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>compliance-check</t>
+          <t>finance-approval</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>step-5</t>
+          <t>step-4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>quality-assurance-review</t>
+          <t>document-verification</t>
         </is>
       </c>
       <c r="B7" s="3">
@@ -1529,40 +1513,40 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Quality Assurance Review</t>
+          <t>Document Verification</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>expense-reimbursement</t>
+          <t>it-support</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>manager</t>
+          <t>contributor</t>
         </is>
       </c>
       <c r="G7" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>quality-assurance</t>
+          <t>compliance-check</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>step-6</t>
+          <t>step-5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>system-notification-sent</t>
+          <t>quality-assurance-review</t>
         </is>
       </c>
       <c r="B8" s="3">
@@ -1571,40 +1555,40 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>System Notification Sent</t>
+          <t>Quality Assurance Review</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>performance-review</t>
+          <t>expense-reimbursement</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="G8" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>final-authorization</t>
+          <t>quality-assurance</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>step-7</t>
+          <t>step-6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>final-approval</t>
+          <t>system-notification-sent</t>
         </is>
       </c>
       <c r="B9" s="3">
@@ -1613,40 +1597,40 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Final Approval</t>
+          <t>System Notification Sent</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>procurement</t>
+          <t>performance-review</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>analyst</t>
+          <t>support</t>
         </is>
       </c>
       <c r="G9" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>manager-approval</t>
+          <t>final-authorization</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>step-8</t>
+          <t>step-7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>archive-request</t>
+          <t>final-approval</t>
         </is>
       </c>
       <c r="B10" s="3">
@@ -1655,40 +1639,40 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Archive Request</t>
+          <t>Final Approval</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>customer-feedback</t>
+          <t>procurement</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>developer</t>
+          <t>analyst</t>
         </is>
       </c>
       <c r="G10" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>it-security-gate</t>
+          <t>manager-approval</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>step-9</t>
+          <t>step-8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>customer-feedback-collection</t>
+          <t>archive-request</t>
         </is>
       </c>
       <c r="B11" s="3">
@@ -1697,20 +1681,20 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Customer Feedback Collection</t>
+          <t>Archive Request</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>project-kickoff</t>
+          <t>customer-feedback</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>tester</t>
+          <t>developer</t>
         </is>
       </c>
       <c r="G11" s="2" t="b">
@@ -1718,19 +1702,19 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>customer-confirmation</t>
+          <t>it-security-gate</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>step-10</t>
+          <t>step-9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>legal-compliance-check</t>
+          <t>customer-feedback-collection</t>
         </is>
       </c>
       <c r="B12" s="3">
@@ -1739,40 +1723,40 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Legal Compliance Check</t>
+          <t>Customer Feedback Collection</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>contract-review</t>
+          <t>project-kickoff</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>tester</t>
         </is>
       </c>
       <c r="G12" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>legal-review</t>
+          <t>customer-confirmation</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>step-11</t>
+          <t>step-10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>assign-task-to-team</t>
+          <t>legal-compliance-check</t>
         </is>
       </c>
       <c r="B13" s="3">
@@ -1781,40 +1765,40 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Assign Task to Team</t>
+          <t>Legal Compliance Check</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>asset-management</t>
+          <t>contract-review</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="G13" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>executive-sign-off</t>
+          <t>legal-review</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>step-12</t>
+          <t>step-11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>some-new-task</t>
+          <t>assign-task-to-team</t>
         </is>
       </c>
       <c r="B14" s="3">
@@ -1823,7 +1807,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Some new task</t>
+          <t>Assign Task to Team</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1832,7 +1816,7 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1844,19 +1828,19 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>some-new-gate</t>
+          <t>executive-sign-off</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>assign-task-to-team</t>
+          <t>step-12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>team-lead-review</t>
+          <t>some-new-task</t>
         </is>
       </c>
       <c r="B15" s="3">
@@ -1865,12 +1849,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Team Lead Review</t>
+          <t>Some new task</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>recruitment</t>
+          <t>asset-management</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
@@ -1878,27 +1862,27 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>guest</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="G15" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>legal-review</t>
+          <t>some-new-gate</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>step-13</t>
+          <t>assign-task-to-team</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>generate-report</t>
+          <t>team-lead-review</t>
         </is>
       </c>
       <c r="B16" s="3">
@@ -1907,40 +1891,40 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Generate Report</t>
+          <t>Team Lead Review</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>incident-reporting</t>
+          <t>recruitment</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>trainer</t>
+          <t>guest</t>
         </is>
       </c>
       <c r="G16" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>finance-approval</t>
+          <t>legal-review</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>step-14</t>
+          <t>step-13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>close-workflow</t>
+          <t>generate-report</t>
         </is>
       </c>
       <c r="B17" s="3">
@@ -1949,20 +1933,20 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Close Workflow</t>
+          <t>Generate Report</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>change-management</t>
+          <t>incident-reporting</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>owner</t>
+          <t>trainer</t>
         </is>
       </c>
       <c r="G17" s="2" t="b">
@@ -1970,14 +1954,146 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>step-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>close-workflow</t>
+        </is>
+      </c>
+      <c r="B18" s="3">
+        <f>SUBSTITUTE(LOWER($C18), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Close Workflow</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>change-management</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
           <t>executive-sign-off</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>step-15</t>
         </is>
       </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>step1</t>
+        </is>
+      </c>
+      <c r="B19" s="3">
+        <f>SUBSTITUTE(LOWER($C19), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>step1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>change-management</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>asdf</t>
+        </is>
+      </c>
+      <c r="B20" s="3">
+        <f>SUBSTITUTE(LOWER($C20), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>asdf</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>change-management</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>step-2</t>
+        </is>
+      </c>
+      <c r="B21" s="3">
+        <f>SUBSTITUTE(LOWER($C21), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Step 2</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>performance-review</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2307,9 +2423,9 @@
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2325,17 +2441,17 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>WorkflowStep</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>DisplayName</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>StepNumber</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>WorkflowStep</t>
         </is>
       </c>
     </row>
@@ -2350,17 +2466,17 @@
           <t>step-1</t>
         </is>
       </c>
-      <c r="C2" s="3">
-        <f>"Step-" &amp; $D2</f>
-        <v/>
-      </c>
-      <c r="D2" s="2" t="n">
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>submit-request</t>
+        </is>
+      </c>
+      <c r="D2" s="3">
+        <f>"Step-" &amp; $E2</f>
+        <v/>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>submit-request</t>
-        </is>
       </c>
     </row>
     <row r="3">
@@ -2374,17 +2490,17 @@
           <t>step-2</t>
         </is>
       </c>
-      <c r="C3" s="3">
-        <f>"Step-" &amp; $D3</f>
-        <v/>
-      </c>
-      <c r="D3" s="2" t="n">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>manager-review</t>
+        </is>
+      </c>
+      <c r="D3" s="3">
+        <f>"Step-" &amp; $E3</f>
+        <v/>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>manager-review</t>
-        </is>
       </c>
     </row>
     <row r="4">
@@ -2398,17 +2514,17 @@
           <t>step-3</t>
         </is>
       </c>
-      <c r="C4" s="3">
-        <f>"Step-" &amp; $D4</f>
-        <v/>
-      </c>
-      <c r="D4" s="2" t="n">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>automated-eligibility-check</t>
+        </is>
+      </c>
+      <c r="D4" s="3">
+        <f>"Step-" &amp; $E4</f>
+        <v/>
+      </c>
+      <c r="E4" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>automated-eligibility-check</t>
-        </is>
       </c>
     </row>
     <row r="5">
@@ -2422,17 +2538,17 @@
           <t>step-4</t>
         </is>
       </c>
-      <c r="C5" s="3">
-        <f>"Step-" &amp; $D5</f>
-        <v/>
-      </c>
-      <c r="D5" s="2" t="n">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="D5" s="3">
+        <f>"Step-" &amp; $E5</f>
+        <v/>
+      </c>
+      <c r="E5" s="2" t="n">
         <v>4</v>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>finance-approval</t>
-        </is>
       </c>
     </row>
     <row r="6">
@@ -2446,17 +2562,17 @@
           <t>step-5</t>
         </is>
       </c>
-      <c r="C6" s="3">
-        <f>"Step-" &amp; $D6</f>
-        <v/>
-      </c>
-      <c r="D6" s="2" t="n">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>document-verification</t>
+        </is>
+      </c>
+      <c r="D6" s="3">
+        <f>"Step-" &amp; $E6</f>
+        <v/>
+      </c>
+      <c r="E6" s="2" t="n">
         <v>5</v>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>document-verification</t>
-        </is>
       </c>
     </row>
     <row r="7">
@@ -2470,17 +2586,17 @@
           <t>step-6</t>
         </is>
       </c>
-      <c r="C7" s="3">
-        <f>"Step-" &amp; $D7</f>
-        <v/>
-      </c>
-      <c r="D7" s="2" t="n">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance-review</t>
+        </is>
+      </c>
+      <c r="D7" s="3">
+        <f>"Step-" &amp; $E7</f>
+        <v/>
+      </c>
+      <c r="E7" s="2" t="n">
         <v>6</v>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>quality-assurance-review</t>
-        </is>
       </c>
     </row>
     <row r="8">
@@ -2494,17 +2610,17 @@
           <t>step-7</t>
         </is>
       </c>
-      <c r="C8" s="3">
-        <f>"Step-" &amp; $D8</f>
-        <v/>
-      </c>
-      <c r="D8" s="2" t="n">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>system-notification-sent</t>
+        </is>
+      </c>
+      <c r="D8" s="3">
+        <f>"Step-" &amp; $E8</f>
+        <v/>
+      </c>
+      <c r="E8" s="2" t="n">
         <v>7</v>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>system-notification-sent</t>
-        </is>
       </c>
     </row>
     <row r="9">
@@ -2518,17 +2634,17 @@
           <t>step-8</t>
         </is>
       </c>
-      <c r="C9" s="3">
-        <f>"Step-" &amp; $D9</f>
-        <v/>
-      </c>
-      <c r="D9" s="2" t="n">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>final-approval</t>
+        </is>
+      </c>
+      <c r="D9" s="3">
+        <f>"Step-" &amp; $E9</f>
+        <v/>
+      </c>
+      <c r="E9" s="2" t="n">
         <v>8</v>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>final-approval</t>
-        </is>
       </c>
     </row>
     <row r="10">
@@ -2542,17 +2658,17 @@
           <t>step-9</t>
         </is>
       </c>
-      <c r="C10" s="3">
-        <f>"Step-" &amp; $D10</f>
-        <v/>
-      </c>
-      <c r="D10" s="2" t="n">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>archive-request</t>
+        </is>
+      </c>
+      <c r="D10" s="3">
+        <f>"Step-" &amp; $E10</f>
+        <v/>
+      </c>
+      <c r="E10" s="2" t="n">
         <v>9</v>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>archive-request</t>
-        </is>
       </c>
     </row>
     <row r="11">
@@ -2566,17 +2682,17 @@
           <t>step-10</t>
         </is>
       </c>
-      <c r="C11" s="3">
-        <f>"Step-" &amp; $D11</f>
-        <v/>
-      </c>
-      <c r="D11" s="2" t="n">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>customer-feedback-collection</t>
+        </is>
+      </c>
+      <c r="D11" s="3">
+        <f>"Step-" &amp; $E11</f>
+        <v/>
+      </c>
+      <c r="E11" s="2" t="n">
         <v>10</v>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>customer-feedback-collection</t>
-        </is>
       </c>
     </row>
     <row r="12">
@@ -2590,17 +2706,17 @@
           <t>step-11</t>
         </is>
       </c>
-      <c r="C12" s="3">
-        <f>"Step-" &amp; $D12</f>
-        <v/>
-      </c>
-      <c r="D12" s="2" t="n">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>legal-compliance-check</t>
+        </is>
+      </c>
+      <c r="D12" s="3">
+        <f>"Step-" &amp; $E12</f>
+        <v/>
+      </c>
+      <c r="E12" s="2" t="n">
         <v>11</v>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>legal-compliance-check</t>
-        </is>
       </c>
     </row>
     <row r="13">
@@ -2614,17 +2730,17 @@
           <t>step-12</t>
         </is>
       </c>
-      <c r="C13" s="3">
-        <f>"Step-" &amp; $D13</f>
-        <v/>
-      </c>
-      <c r="D13" s="2" t="n">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>assign-task-to-team</t>
+        </is>
+      </c>
+      <c r="D13" s="3">
+        <f>"Step-" &amp; $E13</f>
+        <v/>
+      </c>
+      <c r="E13" s="2" t="n">
         <v>12</v>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>assign-task-to-team</t>
-        </is>
       </c>
     </row>
     <row r="14">
@@ -2638,17 +2754,17 @@
           <t>step-13</t>
         </is>
       </c>
-      <c r="C14" s="3">
-        <f>"Step-" &amp; $D14</f>
-        <v/>
-      </c>
-      <c r="D14" s="2" t="n">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>team-lead-review</t>
+        </is>
+      </c>
+      <c r="D14" s="3">
+        <f>"Step-" &amp; $E14</f>
+        <v/>
+      </c>
+      <c r="E14" s="2" t="n">
         <v>13</v>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>team-lead-review</t>
-        </is>
       </c>
     </row>
     <row r="15">
@@ -2662,17 +2778,17 @@
           <t>step-14</t>
         </is>
       </c>
-      <c r="C15" s="3">
-        <f>"Step-" &amp; $D15</f>
-        <v/>
-      </c>
-      <c r="D15" s="2" t="n">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>generate-report</t>
+        </is>
+      </c>
+      <c r="D15" s="3">
+        <f>"Step-" &amp; $E15</f>
+        <v/>
+      </c>
+      <c r="E15" s="2" t="n">
         <v>14</v>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>generate-report</t>
-        </is>
       </c>
     </row>
     <row r="16">
@@ -2686,17 +2802,17 @@
           <t>step-15</t>
         </is>
       </c>
-      <c r="C16" s="3">
-        <f>"Step-" &amp; $D16</f>
-        <v/>
-      </c>
-      <c r="D16" s="2" t="n">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>close-workflow</t>
+        </is>
+      </c>
+      <c r="D16" s="3">
+        <f>"Step-" &amp; $E16</f>
+        <v/>
+      </c>
+      <c r="E16" s="2" t="n">
         <v>15</v>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>close-workflow</t>
-        </is>
       </c>
     </row>
     <row r="17">
@@ -2710,17 +2826,17 @@
           <t>assign-task-to-team</t>
         </is>
       </c>
-      <c r="C17" s="3">
-        <f>"Step-" &amp; $D17</f>
-        <v/>
-      </c>
-      <c r="D17" s="2" t="n">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>some-new-task</t>
+        </is>
+      </c>
+      <c r="D17" s="3">
+        <f>"Step-" &amp; $E17</f>
+        <v/>
+      </c>
+      <c r="E17" s="2" t="n">
         <v>16</v>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>some-new-task</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/execution-substrates/xlsx/rulebook.xlsx
+++ b/execution-substrates/xlsx/rulebook.xlsx
@@ -7,7 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Customers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Workflows" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="WorkflowSteps" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ApprovalGates" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="PrecedesSteps" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Roles" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Departments" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="HumanAgents" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="AIAgents" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="AutomatedPipelines" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,140 +448,5270 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>WorkflowId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WorkflowSteps</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CountOfNonProposedSteps</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>HasMoreThan1Step</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>performance-review</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>SUBSTITUTE(LOWER($C2), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Performance Review</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Annual Performance Review</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Structured workflow for conducting annual employee performance evaluations.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>WF-PRV-007</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>system-notification-sent, step-2, recwwXHLqxKPhj6Mt</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" s="3">
+        <f>$I2 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>change-management</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>SUBSTITUTE(LOWER($C3), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Change Management</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Change Management Workflow</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Structured process for requesting, evaluating, and implementing organizational changes.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>WF-CHM-015</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-27</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>close-workflow, step1, asdf</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" s="3">
+        <f>$I3 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>asset-management</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>SUBSTITUTE(LOWER($C4), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Asset Management</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Asset Management Process</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Process for tracking, maintaining, and auditing company assets.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>WF-ASM-012</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>assign-task-to-team, some-new-task</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" s="3">
+        <f>$I4 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>incident-reporting</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>SUBSTITUTE(LOWER($C5), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Incident Reporting</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Incident Reporting Process</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Steps for reporting, investigating, and resolving workplace incidents.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>WF-INC-014</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>generate-report</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="3">
+        <f>$I5 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>customer-feedback</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>SUBSTITUTE(LOWER($C6), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Customer Feedback</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Customer Feedback Collection</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Workflow for collecting, analyzing, and acting on customer feedback.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>WF-CFB-009</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-25</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>archive-request</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="3">
+        <f>$I6 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>project-kickoff</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>SUBSTITUTE(LOWER($C7), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Project Kickoff</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Project Kickoff Process</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Steps to initiate a new project, including team assignment and goal setting.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>WF-PKO-010</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-20</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>customer-feedback-collection</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="3">
+        <f>$I7 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>onboarding</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>SUBSTITUTE(LOWER($C8), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Employee Onboarding</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>A step-by-step process to onboard new employees, including document collection, orientation, and training.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>WF-ONB-001</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>submit-request</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="3">
+        <f>$I8 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>content-publishing</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>SUBSTITUTE(LOWER($C9), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Content Publishing</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Content Publishing Process</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Workflow for drafting, reviewing, and publishing content to the company website.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>WF-CNT-003</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>automated-eligibility-check</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="3">
+        <f>$I9 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>expense-reimbursement</t>
+        </is>
+      </c>
+      <c r="B10" s="3">
+        <f>SUBSTITUTE(LOWER($C10), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Expense Reimbursement</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Expense Reimbursement Process</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Steps for employees to submit expenses and receive reimbursements after approval.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>WF-EXP-006</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance-review</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="3">
+        <f>$I10 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>procurement</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>SUBSTITUTE(LOWER($C11), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Workflow</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Process for requesting, approving, and purchasing goods or services.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>WF-PRC-008</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-02</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>final-approval</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="3">
+        <f>$I11 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>invoice-approval</t>
+        </is>
+      </c>
+      <c r="B12" s="3">
+        <f>SUBSTITUTE(LOWER($C12), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Approval</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Approval Workflow</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Automated workflow for reviewing, approving, and processing vendor invoices.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>WF-INV-002</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>manager-review</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="3">
+        <f>$I12 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>contract-review</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>SUBSTITUTE(LOWER($C13), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Contract Review</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Contract Review Workflow</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Workflow for legal and management review of contracts before signing.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>WF-CTR-011</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>legal-compliance-check</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="3">
+        <f>$I13 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="B14" s="3">
+        <f>SUBSTITUTE(LOWER($C14), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Recruitment</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Recruitment Workflow</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Workflow for posting jobs, screening candidates, and scheduling interviews.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>WF-RCT-013</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>team-lead-review</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="3">
+        <f>$I14 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>it-support</t>
+        </is>
+      </c>
+      <c r="B15" s="3">
+        <f>SUBSTITUTE(LOWER($C15), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>IT Support</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>IT Support Ticketing</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Workflow for submitting, triaging, and resolving IT support tickets.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>WF-ITS-005</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>document-verification</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="3">
+        <f>$I15 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>leave-request</t>
+        </is>
+      </c>
+      <c r="B16" s="3">
+        <f>SUBSTITUTE(LOWER($C16), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Leave Request</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Leave Request Workflow</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Process for employees to submit, review, and approve leave requests.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>WF-LRQ-004</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="3">
+        <f>$I16 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>WorkflowStepId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Workflow</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>SequencePosition</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>AssignedRole</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>RequiresHumanApproval</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ApprovalGate</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>PrecededBySteps</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>submit-request</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>SUBSTITUTE(LOWER($C2), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Submit Request</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>onboarding</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>initial-review</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>step-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>manager-review</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>SUBSTITUTE(LOWER($C3), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Manager Review</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>invoice-approval</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>manager-approval</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>step-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>recwwXHLqxKPhj6Mt</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>SUBSTITUTE(LOWER($C4), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>performance-review</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>automated-eligibility-check</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>SUBSTITUTE(LOWER($C5), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Automated Eligibility Check</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>content-publishing</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>it-security-gate</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>step-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>SUBSTITUTE(LOWER($C6), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Finance Approval</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>leave-request</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>step-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>document-verification</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>SUBSTITUTE(LOWER($C7), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Document Verification</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>it-support</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>compliance-check</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>step-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance-review</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>SUBSTITUTE(LOWER($C8), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Quality Assurance Review</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>expense-reimbursement</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>step-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>system-notification-sent</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>SUBSTITUTE(LOWER($C9), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>System Notification Sent</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>performance-review</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>final-authorization</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>step-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>final-approval</t>
+        </is>
+      </c>
+      <c r="B10" s="3">
+        <f>SUBSTITUTE(LOWER($C10), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Final Approval</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>procurement</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>manager-approval</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>step-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>archive-request</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>SUBSTITUTE(LOWER($C11), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Archive Request</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>customer-feedback</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>it-security-gate</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>step-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>customer-feedback-collection</t>
+        </is>
+      </c>
+      <c r="B12" s="3">
+        <f>SUBSTITUTE(LOWER($C12), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Customer Feedback Collection</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>project-kickoff</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>customer-confirmation</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>step-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>legal-compliance-check</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>SUBSTITUTE(LOWER($C13), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Legal Compliance Check</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>contract-review</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>legal-review</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>step-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>assign-task-to-team</t>
+        </is>
+      </c>
+      <c r="B14" s="3">
+        <f>SUBSTITUTE(LOWER($C14), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Assign Task to Team</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>asset-management</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>executive-sign-off</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>step-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>some-new-task</t>
+        </is>
+      </c>
+      <c r="B15" s="3">
+        <f>SUBSTITUTE(LOWER($C15), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Some new task</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>asset-management</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>some-new-gate</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>assign-task-to-team</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>team-lead-review</t>
+        </is>
+      </c>
+      <c r="B16" s="3">
+        <f>SUBSTITUTE(LOWER($C16), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Team Lead Review</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>legal-review</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>step-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>generate-report</t>
+        </is>
+      </c>
+      <c r="B17" s="3">
+        <f>SUBSTITUTE(LOWER($C17), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Generate Report</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>incident-reporting</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>step-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>close-workflow</t>
+        </is>
+      </c>
+      <c r="B18" s="3">
+        <f>SUBSTITUTE(LOWER($C18), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Close Workflow</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>change-management</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>executive-sign-off</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>step-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>step1</t>
+        </is>
+      </c>
+      <c r="B19" s="3">
+        <f>SUBSTITUTE(LOWER($C19), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>step1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>change-management</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>asdf</t>
+        </is>
+      </c>
+      <c r="B20" s="3">
+        <f>SUBSTITUTE(LOWER($C20), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>asdf</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>change-management</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>step-2</t>
+        </is>
+      </c>
+      <c r="B21" s="3">
+        <f>SUBSTITUTE(LOWER($C21), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Step 2</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>performance-review</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ApprovalGateId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>WorkflowSteps</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>EscalationThresholdHours</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>initial-review</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>SUBSTITUTE(LOWER($C2), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Initial Review</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>submit-request</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>manager-approval</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>SUBSTITUTE(LOWER($C3), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Manager Approval</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>final-approval, manager-review</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>compliance-check</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>SUBSTITUTE(LOWER($C4), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Compliance Check</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>document-verification</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>final-authorization</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>SUBSTITUTE(LOWER($C5), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Final Authorization</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>system-notification-sent</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>executive-sign-off</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>SUBSTITUTE(LOWER($C6), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Executive Sign-off</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>close-workflow, assign-task-to-team</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>SUBSTITUTE(LOWER($C7), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Quality Assurance</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance-review</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>legal-review</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>SUBSTITUTE(LOWER($C8), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Legal Review</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>team-lead-review, legal-compliance-check</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>SUBSTITUTE(LOWER($C9), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Finance Approval</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>generate-report, finance-approval</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>it-security-gate</t>
+        </is>
+      </c>
+      <c r="B10" s="3">
+        <f>SUBSTITUTE(LOWER($C10), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>IT Security Gate</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>archive-request, automated-eligibility-check</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>customer-confirmation</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>SUBSTITUTE(LOWER($C11), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Customer Confirmation</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>customer-feedback-collection</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>some-new-gate</t>
+        </is>
+      </c>
+      <c r="B12" s="3">
+        <f>SUBSTITUTE(LOWER($C12), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>some new gate</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>some-new-task</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PrecedesStepId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>WorkflowStep</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>StepNumber</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>step-1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>step-1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>submit-request</t>
+        </is>
+      </c>
+      <c r="D2" s="3">
+        <f>"Step-" &amp; $E2</f>
+        <v/>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>step-2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>step-2</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>manager-review</t>
+        </is>
+      </c>
+      <c r="D3" s="3">
+        <f>"Step-" &amp; $E3</f>
+        <v/>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>step-3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>step-3</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>automated-eligibility-check</t>
+        </is>
+      </c>
+      <c r="D4" s="3">
+        <f>"Step-" &amp; $E4</f>
+        <v/>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>step-4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>step-4</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="D5" s="3">
+        <f>"Step-" &amp; $E5</f>
+        <v/>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>step-5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>step-5</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>document-verification</t>
+        </is>
+      </c>
+      <c r="D6" s="3">
+        <f>"Step-" &amp; $E6</f>
+        <v/>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>step-6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>step-6</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance-review</t>
+        </is>
+      </c>
+      <c r="D7" s="3">
+        <f>"Step-" &amp; $E7</f>
+        <v/>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>step-7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>step-7</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>system-notification-sent</t>
+        </is>
+      </c>
+      <c r="D8" s="3">
+        <f>"Step-" &amp; $E8</f>
+        <v/>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>step-8</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>step-8</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>final-approval</t>
+        </is>
+      </c>
+      <c r="D9" s="3">
+        <f>"Step-" &amp; $E9</f>
+        <v/>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>step-9</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>step-9</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>archive-request</t>
+        </is>
+      </c>
+      <c r="D10" s="3">
+        <f>"Step-" &amp; $E10</f>
+        <v/>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>step-10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>step-10</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>customer-feedback-collection</t>
+        </is>
+      </c>
+      <c r="D11" s="3">
+        <f>"Step-" &amp; $E11</f>
+        <v/>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>step-11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>step-11</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>legal-compliance-check</t>
+        </is>
+      </c>
+      <c r="D12" s="3">
+        <f>"Step-" &amp; $E12</f>
+        <v/>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>step-12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>step-12</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>assign-task-to-team</t>
+        </is>
+      </c>
+      <c r="D13" s="3">
+        <f>"Step-" &amp; $E13</f>
+        <v/>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>step-13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>step-13</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>team-lead-review</t>
+        </is>
+      </c>
+      <c r="D14" s="3">
+        <f>"Step-" &amp; $E14</f>
+        <v/>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>step-14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>step-14</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>generate-report</t>
+        </is>
+      </c>
+      <c r="D15" s="3">
+        <f>"Step-" &amp; $E15</f>
+        <v/>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>step-15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>step-15</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>close-workflow</t>
+        </is>
+      </c>
+      <c r="D16" s="3">
+        <f>"Step-" &amp; $E16</f>
+        <v/>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>assign-task-to-team</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>assign-task-to-team</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>some-new-task</t>
+        </is>
+      </c>
+      <c r="D17" s="3">
+        <f>"Step-" &amp; $E17</f>
+        <v/>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>RoleId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>FilledByHumanAgent</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>FilledByAIAgent</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>FilledByAutomatedPipeline</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>OwnedBy</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>DelegatesTo</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WorkflowSteps</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>FromDelegatesTo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>LOWER($C2)</f>
+        <v/>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Has full access to all system features and settings.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>agent-001</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>ava</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>lead-notification-pipeline</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>human-resources</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>submit-request</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>LOWER($C3)</f>
+        <v/>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Editor</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Content Editor</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Can create, edit, and delete content but cannot change system settings.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>agent-002</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>leo</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>e-commerce-order-sync</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>manager-review</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>LOWER($C4)</f>
+        <v/>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Viewer</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Read-Only</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Can view content but cannot make any changes.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>agent-003</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>maya</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>issue-tracking-bridge</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>information-technology</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>automated-eligibility-check</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>LOWER($C5)</f>
+        <v/>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Moderator</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Forum Moderator</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Can manage user comments and moderate discussions.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>agent-004</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>newsletter-signup-sync</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>marketing</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>LOWER($C6)</f>
+        <v/>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Contributor</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Content Contributor</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Can submit new content for review but cannot publish directly.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>agent-005</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>zara</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>support-ticket-automation</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>document-verification</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>LOWER($C7)</f>
+        <v/>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Oversees project progress and manages team assignments.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>agent-006</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>owen</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>devops-integration</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>customer-service</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance-review</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>LOWER($C8)</f>
+        <v/>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Customer Support</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Handles user inquiries and provides technical assistance.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>agent-007</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>nina</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>finance-automation</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>research-and-development</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>system-notification-sent</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>LOWER($C9)</f>
+        <v/>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Has access to analytics and reporting tools.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>agent-008</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>kai</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>project-intake-pipeline</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>legal</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>final-approval</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+      <c r="B10" s="3">
+        <f>LOWER($C10)</f>
+        <v/>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Can access and modify application code and integrations.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>agent-009</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>sophie</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>crm-data-sync</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>procurement</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>archive-request</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>LOWER($C11)</f>
+        <v/>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Quality Assurance</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Responsible for testing new features and reporting bugs.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>agent-010</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>calendar-integration</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>customer-feedback-collection</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="B12" s="3">
+        <f>LOWER($C12)</f>
+        <v/>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Human Resources</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Manages employee records and recruitment processes.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>agent-011</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>liam</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>survey-data-pipeline</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>legal-compliance-check</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>LOWER($C13)</f>
+        <v/>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Finance Officer</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Handles billing, invoices, and financial reports.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>agent-012</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>jade</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>task-management-sync</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>public-relations</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>assign-task-to-team, some-new-task</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B14" s="3">
+        <f>LOWER($C14)</f>
+        <v/>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Temporary Access</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Limited access for temporary users or external collaborators.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>agent-013</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>mila</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>cloud-storage-sync</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>team-lead-review</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+      <c r="B15" s="3">
+        <f>LOWER($C15)</f>
+        <v/>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Training Specialist</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Creates and delivers training materials to users.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>agent-014</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>noah</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>email-notification-pipeline</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>facilities-management</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>generate-report</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="B16" s="3">
+        <f>LOWER($C16)</f>
+        <v/>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>System Owner</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Ultimate authority over the system, can assign or revoke any role.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>agent-015</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>ella</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>survey-data-export</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>training-and-development</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>close-workflow</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DepartmentId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>human-resources</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>SUBSTITUTE(LOWER($D2), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>HR Department</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Human Resources</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>SUBSTITUTE(LOWER($D3), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Finance Department</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>information-technology</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>SUBSTITUTE(LOWER($D4), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>IT Department</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>marketing</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>SUBSTITUTE(LOWER($D5), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Department</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>SUBSTITUTE(LOWER($D6), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Sales Department</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>customer-service</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>SUBSTITUTE(LOWER($D7), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Customer Service Department</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Customer Service</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>research-and-development</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>SUBSTITUTE(LOWER($D8), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>R&amp;D Department</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Research and Development</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>legal</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>SUBSTITUTE(LOWER($D9), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Legal Department</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>procurement</t>
+        </is>
+      </c>
+      <c r="B10" s="3">
+        <f>SUBSTITUTE(LOWER($D10), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Department</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>SUBSTITUTE(LOWER($D11), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Operations Department</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
+      <c r="B12" s="3">
+        <f>SUBSTITUTE(LOWER($D12), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Administration Department</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>public-relations</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>SUBSTITUTE(LOWER($D13), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>PR Department</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Public Relations</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance</t>
+        </is>
+      </c>
+      <c r="B14" s="3">
+        <f>SUBSTITUTE(LOWER($D14), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>QA Department</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Quality Assurance</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>facilities-management</t>
+        </is>
+      </c>
+      <c r="B15" s="3">
+        <f>SUBSTITUTE(LOWER($D15), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Facilities Department</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Facilities Management</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>training-and-development</t>
+        </is>
+      </c>
+      <c r="B16" s="3">
+        <f>SUBSTITUTE(LOWER($D16), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Training Department</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Training and Development</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>HumanAgentId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Mbox</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>agent-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>agent_001</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Alice Johnson</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>alice.johnson@example.com</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>agent-002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>agent_002</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Brian Smith</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>brian.smith@example.com</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>agent-003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>agent_003</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Catherine Lee</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>catherine.lee@example.com</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>agent-004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>agent_004</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>David Kim</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>david.kim@example.com</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>agent-005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>agent_005</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Emily Chen</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>emily.chen@example.com</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>agent-006</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>agent_006</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Frank Miller</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>frank.miller@example.com</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>agent-007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>agent_007</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Grace Park</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>grace.park@example.com</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>agent-008</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>agent_008</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Henry Adams</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>henry.adams@example.com</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>agent-009</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>agent_009</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Isabella Martinez</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>isabella.martinez@example.com</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>agent-010</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>agent_010</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Jack Wilson</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>jack.wilson@example.com</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>agent-011</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>agent_011</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Karen Patel</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>karen.patel@example.com</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>agent-012</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>agent_012</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Liam Nguyen</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>liam.nguyen@example.com</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>agent-013</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>agent_013</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Monica Rivera</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>monica.rivera@example.com</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>agent-014</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>agent_014</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Nathan Brown</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>nathan.brown@example.com</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>agent-015</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>agent_015</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Olivia Clark</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>olivia.clark@example.com</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CustomerId</t>
+          <t>AIAgentId</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>EmailAddress</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>FirstName</t>
+          <t>DisplayName</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>LastName</t>
+          <t>ModelVersion</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>FullName</t>
+          <t>Roles</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>cust0001</t>
+          <t>ava</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>CUST0001</t>
+          <t>Ava</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>jane.smith@email.com</t>
+          <t>CustomerSupportBot</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Ava</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Smith</t>
-        </is>
-      </c>
-      <c r="F2" s="3">
-        <f>$E2 &amp; ", " &amp; $D2</f>
-        <v/>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>cust0002</t>
+          <t>leo</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CUST0002</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>john.doe@email.com</t>
+          <t>SalesAssistantAI</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Doe</t>
-        </is>
-      </c>
-      <c r="F3" s="3">
-        <f>$E3 &amp; ", " &amp; $D3</f>
-        <v/>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>cust0003</t>
+          <t>maya</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CUST0003</t>
+          <t>Maya</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>emily.jones@email.com</t>
+          <t>HRRecruiterBot</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Maya</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jones</t>
-        </is>
-      </c>
-      <c r="F4" s="3">
-        <f>$E4 &amp; ", " &amp; $D4</f>
-        <v/>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Eli</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>FinanceAdvisorAI</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Eli</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>zara</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Zara</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>MarketingCopyAI</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Zara</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>owen</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Owen</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>LegalDraftBot</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Owen</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>nina</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>MedicalAssistantAI</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>kai</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Kai</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>TravelPlannerBot</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Kai</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>sophie</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Sophie</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>EcommerceHelperAI</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Sophie</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>EducationTutorBot</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>liam</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Liam</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>RealEstateAdvisorAI</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Liam</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>jade</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Jade</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>FitnessCoachBot</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Jade</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>mila</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Mila</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>EventPlannerAI</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Mila</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>noah</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Noah</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>PersonalFinanceBot</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Noah</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ella</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Ella</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>ContentEditorAI</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Ella</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>AutomatedPipelineId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>lead-notification-pipeline</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>lead-notification-pipeline</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Salesforce to Slack Lead Alert</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Lead Notification Pipeline</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>e-commerce-order-sync</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>e-commerce-order-sync</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Shopify Order to QuickBooks Invoice</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>E-commerce Order Sync</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>issue-tracking-bridge</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>issue-tracking-bridge</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Jira Issue to Trello Card</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Issue Tracking Bridge</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>newsletter-signup-sync</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>newsletter-signup-sync</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Google Sheets to Mailchimp Subscriber</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Newsletter Signup Sync</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>support-ticket-automation</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>support-ticket-automation</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Zendesk Ticket to Asana Task</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Support Ticket Automation</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>devops-integration</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>devops-integration</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>GitHub PR to Jira Story</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>DevOps Integration</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>finance-automation</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>finance-automation</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Stripe Payment to Xero Invoice</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Finance Automation</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>project-intake-pipeline</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>project-intake-pipeline</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Airtable Form to Monday.com Item</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Project Intake Pipeline</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>crm-data-sync</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>crm-data-sync</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>HubSpot Contact to Salesforce Lead</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>CRM Data Sync</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>calendar-integration</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>calendar-integration</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Google Calendar Event to Teams Meeting</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Calendar Integration</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>survey-data-pipeline</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>survey-data-pipeline</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Typeform Response to Notion Database</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Survey Data Pipeline</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>task-management-sync</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>task-management-sync</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Trello Card to Google Tasks</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Task Management Sync</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>cloud-storage-sync</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>cloud-storage-sync</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Dropbox Upload to Google Drive</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Storage Sync</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>email-notification-pipeline</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>email-notification-pipeline</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Outlook Email to Slack Channel</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Email Notification Pipeline</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>survey-data-export</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>survey-data-export</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>SurveyMonkey Response to Excel Sheet</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Survey Data Export</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/execution-substrates/xlsx/rulebook.xlsx
+++ b/execution-substrates/xlsx/rulebook.xlsx
@@ -7,7 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Customers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Workflows" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="WorkflowSteps" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ApprovalGates" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="PrecedesSteps" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Roles" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Departments" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="HumanAgents" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="AIAgents" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="AutomatedPipelines" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -149,6 +157,266 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ERB Rulebook</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Short machine-friendly name for the workflow. Used for programmatic reference and URL slug generation.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Human-readable title of the workflow. Maps to dct:title from Dublin Core. Example: 'Production Deployment Workflow', 'Employee Onboarding'.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Detailed description of the workflow's purpose and scope. Maps to dct:description from Dublin Core. Should explain what business goal the workflow achieves.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>External system identifier for cross-referencing. Maps to dct:identifier from Dublin Core. This is the join key back to document management systems, ticket systems, or other operational systems.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Last modification timestamp. Maps to dct:modified from Dublin Core. Critical for answering CQ5: 'Which workflows haven't been reviewed or updated in twelve months?'</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Reference to workflow steps. Represents the ntwf:hasStep relationship linking workflows to their constituent steps.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Calculated count of workflow steps in this workflow. Useful for workflow complexity analysis and reporting.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ERB Rulebook</author>
+  </authors>
+  <commentList>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Foreign key to the parent workflow. Represents the inverse of ntwf:hasStep, enabling navigation from step to its containing workflow (ntwf:isStepOf).</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Integer ordinal position of the step within its workflow. Maps to ntwf:sequencePosition, declared as owl:FunctionalProperty (each step has exactly one position). Enables positional queries.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Foreign key to the Role responsible for executing this step. Maps to ntwf:assignedRole. Critical for implementing Heuristic 2 (role-agent separation): steps point to roles, not directly to agents.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Boolean flag indicating whether a human agent must fill the assigned role. Maps to ntwf:requiresHumanApproval. Enables answering CQ3: 'Which steps require human decisions vs. AI execution?'</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Foreign key to ApprovalGate if this step is a decision checkpoint. When populated, indicates this step blocks workflow execution until explicit authorization is given.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Reference to steps that must complete before this step can execute. Part of the ntwf:precedesStep transitive ordering relationship.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ERB Rulebook</author>
+  </authors>
+  <commentList>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Back-reference to workflow steps that use this approval gate. Enables finding all steps requiring this specific gate.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Integer number of hours that may elapse on a pending gate before the ntwf:delegatesTo chain activates. Maps to ntwf:escalationThresholdHours. Domain applies only to ApprovalGate individuals.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ERB Rulebook</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Ordinal sequence number for the relationship. Used for sorting and display.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Foreign key to the step that comes BEFORE. The source of the 'precedes' relationship.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ERB Rulebook</author>
+  </authors>
+  <commentList>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Human-readable display name. Maps to rdfs:label. Per Heuristic 6: if you cannot write a clear label, you do not yet understand the concept well enough to model it.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Detailed description of the role's responsibilities and scope. Maps to rdfs:comment. Should define what the role covers, what it excludes, and how it differs from adjacent roles.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Foreign key to the Department that owns this role. Maps to ntwf:ownedBy (owl:FunctionalProperty). Enables answering CQ7: 'Which workflows involve both Engineering and Legal?'</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Foreign key to the fallback Role in an escalation chain. Maps to ntwf:delegatesTo. Enables answering CQ6: 'What happens when the VP of Engineering is unavailable?'</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>Back-reference to workflow steps assigned to this role. Inverse of WorkflowSteps.AssignedRole.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ERB Rulebook</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Human-readable display name of the department. Should match organizational terminology for stakeholder communication.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Human-readable display name of the department. Should match organizational terminology for stakeholder communication.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Machine-friendly name for programmatic reference.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Back-reference to roles owned by this department. Inverse of Roles.OwnedBy.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ERB Rulebook</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Full name of the person. Maps to foaf:name. Note: FOAF's name property is appropriate for persons, not for software systems (which use schema:name).</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Email address of the person. Maps to foaf:mbox. Used for notifications and organizational directory integration.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Back-reference to roles currently filled by this agent. Inverse of Roles.FilledBy_HumanAgent.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ERB Rulebook</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Display name of the AI agent. Maps to schema:name (not foaf:name, which is for persons).</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Version string of the AI model. Maps to ntwf:modelVersion. Makes AI-produced artifacts auditable at the version level. The domain declaration means this property applies only to AIAgent individuals.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Back-reference to roles currently filled by this AI agent. Inverse of Roles.FilledBy_AIAgent.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ERB Rulebook</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Display name of the pipeline. Maps to schema:name (appropriate for software systems, unlike foaf:name which is for persons).</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Back-reference to roles currently filled by this pipeline. Inverse of Roles.FilledBy_AutomatedPipeline.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -440,143 +708,5307 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>WorkflowId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>WorkflowSteps</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>CountOfNonProposedSteps</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>HasMoreThan1Step</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>performance-review</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>SUBSTITUTE(LOWER($C2), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Performance Review</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Annual Performance Review</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Structured workflow for conducting annual employee performance evaluations.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>WF-PRV-007</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>system-notification-sent, step-2, recwwXHLqxKPhj6Mt</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" s="3">
+        <f>$J2 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>change-management</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>SUBSTITUTE(LOWER($C3), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Change Management</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Change Management Workflow</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Structured process for requesting, evaluating, and implementing organizational changes.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>WF-CHM-015</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-27</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>close-workflow, step1, asdf</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" s="3">
+        <f>$J3 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>incident-reporting</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>SUBSTITUTE(LOWER($C4), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Incident Reporting</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Incident Reporting Process</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Steps for reporting, investigating, and resolving workplace incidents.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>WF-INC-014</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>generate-report</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="3">
+        <f>$J4 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>customer-feedback</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>SUBSTITUTE(LOWER($C5), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Customer Feedback</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Customer Feedback Collection</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Workflow for collecting, analyzing, and acting on customer feedback.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>WF-CFB-009</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-25</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>archive-request</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="3">
+        <f>$J5 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>project-kickoff</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>SUBSTITUTE(LOWER($C6), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Project Kickoff</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Project Kickoff Process</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Steps to initiate a new project, including team assignment and goal setting.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>WF-PKO-010</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-20</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>customer-feedback-collection</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="3">
+        <f>$J6 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>onboarding</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>SUBSTITUTE(LOWER($C7), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Employee Onboarding</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>A step-by-step process to onboard new employees, including document collection, orientation, and training.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>WF-ONB-001</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>submit-request</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="3">
+        <f>$J7 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>content-publishing</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>SUBSTITUTE(LOWER($C8), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Content Publishing</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Content Publishing Process</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Workflow for drafting, reviewing, and publishing content to the company website.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>WF-CNT-003</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>automated-eligibility-check</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="3">
+        <f>$J8 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>expense-reimbursement</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>SUBSTITUTE(LOWER($C9), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Expense Reimbursement</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Expense Reimbursement Process</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Steps for employees to submit expenses and receive reimbursements after approval.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>WF-EXP-006</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance-review</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="3">
+        <f>$J9 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>procurement</t>
+        </is>
+      </c>
+      <c r="B10" s="3">
+        <f>SUBSTITUTE(LOWER($C10), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Workflow</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Process for requesting, approving, and purchasing goods or services.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>WF-PRC-008</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-02</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>final-approval</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="3">
+        <f>$J10 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>invoice-approval</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>SUBSTITUTE(LOWER($C11), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Approval</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Approval Workflow</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Automated workflow for reviewing, approving, and processing vendor invoices.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>WF-INV-002</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>manager-review</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="3">
+        <f>$J11 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>asset-management</t>
+        </is>
+      </c>
+      <c r="B12" s="3">
+        <f>SUBSTITUTE(LOWER($C12), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Asset Management</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Asset Management Process</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Process for tracking, maintaining, and auditing company assets.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>WF-ASM-012</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>assign-task-to-team</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="3">
+        <f>$J12 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>contract-review</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>SUBSTITUTE(LOWER($C13), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Contract Review</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Contract Review Workflow</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Workflow for legal and management review of contracts before signing.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>WF-CTR-011</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>legal-compliance-check</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="3">
+        <f>$J13 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="B14" s="3">
+        <f>SUBSTITUTE(LOWER($C14), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Recruitment</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Recruitment Workflow</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Workflow for posting jobs, screening candidates, and scheduling interviews.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>WF-RCT-013</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>team-lead-review</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="3">
+        <f>$J14 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>it-support</t>
+        </is>
+      </c>
+      <c r="B15" s="3">
+        <f>SUBSTITUTE(LOWER($C15), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>IT Support</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>IT Support Ticketing</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Workflow for submitting, triaging, and resolving IT support tickets.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>WF-ITS-005</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>document-verification</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="3">
+        <f>$J15 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>leave-request</t>
+        </is>
+      </c>
+      <c r="B16" s="3">
+        <f>SUBSTITUTE(LOWER($C16), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Leave Request</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Leave Request Workflow</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Process for employees to submit, review, and approve leave requests.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>WF-LRQ-004</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="3">
+        <f>$J16 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>WorkflowStepId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Workflow</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>SequencePosition</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>AssignedRole</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>RequiresHumanApproval</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ApprovalGate</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>PrecededBySteps</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>submit-request</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>SUBSTITUTE(LOWER($C2), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Submit Request</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>onboarding</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>initial-review</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>step-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>manager-review</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>SUBSTITUTE(LOWER($C3), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Manager Review</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>invoice-approval</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>manager-approval</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>step-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>recwwXHLqxKPhj6Mt</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>SUBSTITUTE(LOWER($C4), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>performance-review</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>automated-eligibility-check</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>SUBSTITUTE(LOWER($C5), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Automated Eligibility Check</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>content-publishing</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>it-security-gate</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>step-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>SUBSTITUTE(LOWER($C6), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Finance Approval</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>leave-request</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>step-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>document-verification</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>SUBSTITUTE(LOWER($C7), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Document Verification</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>it-support</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>compliance-check</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>step-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance-review</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>SUBSTITUTE(LOWER($C8), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Quality Assurance Review</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>expense-reimbursement</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>step-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>system-notification-sent</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>SUBSTITUTE(LOWER($C9), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>System Notification Sent</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>performance-review</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>final-authorization</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>step-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>final-approval</t>
+        </is>
+      </c>
+      <c r="B10" s="3">
+        <f>SUBSTITUTE(LOWER($C10), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Final Approval</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>procurement</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>manager-approval</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>step-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>archive-request</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>SUBSTITUTE(LOWER($C11), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Archive Request</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>customer-feedback</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>it-security-gate</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>step-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>customer-feedback-collection</t>
+        </is>
+      </c>
+      <c r="B12" s="3">
+        <f>SUBSTITUTE(LOWER($C12), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Customer Feedback Collection</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>project-kickoff</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>customer-confirmation</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>step-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>legal-compliance-check</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>SUBSTITUTE(LOWER($C13), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Legal Compliance Check</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>contract-review</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>legal-review</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>step-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>assign-task-to-team</t>
+        </is>
+      </c>
+      <c r="B14" s="3">
+        <f>SUBSTITUTE(LOWER($C14), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Assign Task to Team</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>asset-management</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>executive-sign-off</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>step-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>some-new-task</t>
+        </is>
+      </c>
+      <c r="B15" s="3">
+        <f>SUBSTITUTE(LOWER($C15), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Some new task</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>some-new-gate</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>assign-task-to-team</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>team-lead-review</t>
+        </is>
+      </c>
+      <c r="B16" s="3">
+        <f>SUBSTITUTE(LOWER($C16), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Team Lead Review</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>legal-review</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>step-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>generate-report</t>
+        </is>
+      </c>
+      <c r="B17" s="3">
+        <f>SUBSTITUTE(LOWER($C17), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Generate Report</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>incident-reporting</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>step-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>close-workflow</t>
+        </is>
+      </c>
+      <c r="B18" s="3">
+        <f>SUBSTITUTE(LOWER($C18), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Close Workflow</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>change-management</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>executive-sign-off</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>step-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>step1</t>
+        </is>
+      </c>
+      <c r="B19" s="3">
+        <f>SUBSTITUTE(LOWER($C19), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>step1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>change-management</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>asdf</t>
+        </is>
+      </c>
+      <c r="B20" s="3">
+        <f>SUBSTITUTE(LOWER($C20), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>asdf</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>change-management</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>step-2</t>
+        </is>
+      </c>
+      <c r="B21" s="3">
+        <f>SUBSTITUTE(LOWER($C21), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Step 2</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>performance-review</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ApprovalGateId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>WorkflowSteps</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>EscalationThresholdHours</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>initial-review</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>SUBSTITUTE(LOWER($C2), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Initial Review</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>submit-request</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>manager-approval</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>SUBSTITUTE(LOWER($C3), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Manager Approval</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>final-approval, manager-review</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>compliance-check</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>SUBSTITUTE(LOWER($C4), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Compliance Check</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>document-verification</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>final-authorization</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>SUBSTITUTE(LOWER($C5), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Final Authorization</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>system-notification-sent</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>executive-sign-off</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>SUBSTITUTE(LOWER($C6), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Executive Sign-off</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>close-workflow, assign-task-to-team</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>SUBSTITUTE(LOWER($C7), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Quality Assurance</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance-review</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>legal-review</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>SUBSTITUTE(LOWER($C8), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Legal Review</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>team-lead-review, legal-compliance-check</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>SUBSTITUTE(LOWER($C9), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Finance Approval</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>generate-report, finance-approval</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>it-security-gate</t>
+        </is>
+      </c>
+      <c r="B10" s="3">
+        <f>SUBSTITUTE(LOWER($C10), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>IT Security Gate</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>archive-request, automated-eligibility-check</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>customer-confirmation</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>SUBSTITUTE(LOWER($C11), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Customer Confirmation</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>customer-feedback-collection</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>some-new-gate</t>
+        </is>
+      </c>
+      <c r="B12" s="3">
+        <f>SUBSTITUTE(LOWER($C12), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>some new gate</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>some-new-task</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PrecedesStepId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>WorkflowStep</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>StepNumber</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>step-1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>step-1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>submit-request</t>
+        </is>
+      </c>
+      <c r="D2" s="3">
+        <f>"Step-" &amp; $E2</f>
+        <v/>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>step-2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>step-2</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>manager-review</t>
+        </is>
+      </c>
+      <c r="D3" s="3">
+        <f>"Step-" &amp; $E3</f>
+        <v/>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>step-3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>step-3</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>automated-eligibility-check</t>
+        </is>
+      </c>
+      <c r="D4" s="3">
+        <f>"Step-" &amp; $E4</f>
+        <v/>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>step-4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>step-4</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="D5" s="3">
+        <f>"Step-" &amp; $E5</f>
+        <v/>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>step-5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>step-5</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>document-verification</t>
+        </is>
+      </c>
+      <c r="D6" s="3">
+        <f>"Step-" &amp; $E6</f>
+        <v/>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>step-6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>step-6</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance-review</t>
+        </is>
+      </c>
+      <c r="D7" s="3">
+        <f>"Step-" &amp; $E7</f>
+        <v/>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>step-7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>step-7</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>system-notification-sent</t>
+        </is>
+      </c>
+      <c r="D8" s="3">
+        <f>"Step-" &amp; $E8</f>
+        <v/>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>step-8</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>step-8</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>final-approval</t>
+        </is>
+      </c>
+      <c r="D9" s="3">
+        <f>"Step-" &amp; $E9</f>
+        <v/>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>step-9</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>step-9</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>archive-request</t>
+        </is>
+      </c>
+      <c r="D10" s="3">
+        <f>"Step-" &amp; $E10</f>
+        <v/>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>step-10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>step-10</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>customer-feedback-collection</t>
+        </is>
+      </c>
+      <c r="D11" s="3">
+        <f>"Step-" &amp; $E11</f>
+        <v/>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>step-11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>step-11</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>legal-compliance-check</t>
+        </is>
+      </c>
+      <c r="D12" s="3">
+        <f>"Step-" &amp; $E12</f>
+        <v/>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>step-12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>step-12</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>assign-task-to-team</t>
+        </is>
+      </c>
+      <c r="D13" s="3">
+        <f>"Step-" &amp; $E13</f>
+        <v/>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>step-13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>step-13</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>team-lead-review</t>
+        </is>
+      </c>
+      <c r="D14" s="3">
+        <f>"Step-" &amp; $E14</f>
+        <v/>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>step-14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>step-14</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>generate-report</t>
+        </is>
+      </c>
+      <c r="D15" s="3">
+        <f>"Step-" &amp; $E15</f>
+        <v/>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>step-15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>step-15</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>close-workflow</t>
+        </is>
+      </c>
+      <c r="D16" s="3">
+        <f>"Step-" &amp; $E16</f>
+        <v/>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>assign-task-to-team</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>assign-task-to-team</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>some-new-task</t>
+        </is>
+      </c>
+      <c r="D17" s="3">
+        <f>"Step-" &amp; $E17</f>
+        <v/>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>RoleId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>FilledByHumanAgent</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>FilledByAIAgent</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>FilledByAutomatedPipeline</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>OwnedBy</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>DelegatesTo</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WorkflowSteps</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>FromDelegatesTo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>LOWER($C2)</f>
+        <v/>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Has full access to all system features and settings.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>agent-001</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>ava</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>lead-notification-pipeline</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>human-resources</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>submit-request</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>LOWER($C3)</f>
+        <v/>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Editor</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Content Editor</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Can create, edit, and delete content but cannot change system settings.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>agent-002</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>leo</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>e-commerce-order-sync</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>manager-review</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>LOWER($C4)</f>
+        <v/>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Viewer</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Read-Only</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Can view content but cannot make any changes.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>agent-003</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>maya</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>issue-tracking-bridge</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>information-technology</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>automated-eligibility-check</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>LOWER($C5)</f>
+        <v/>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Moderator</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Forum Moderator</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Can manage user comments and moderate discussions.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>agent-004</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>newsletter-signup-sync</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>marketing</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>LOWER($C6)</f>
+        <v/>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Contributor</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Content Contributor</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Can submit new content for review but cannot publish directly.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>agent-005</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>zara</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>support-ticket-automation</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>document-verification</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>LOWER($C7)</f>
+        <v/>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Oversees project progress and manages team assignments.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>agent-006</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>owen</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>devops-integration</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>customer-service</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance-review</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>LOWER($C8)</f>
+        <v/>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Customer Support</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Handles user inquiries and provides technical assistance.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>agent-007</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>nina</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>finance-automation</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>research-and-development</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>system-notification-sent</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>LOWER($C9)</f>
+        <v/>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Has access to analytics and reporting tools.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>agent-008</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>kai</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>project-intake-pipeline</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>legal</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>final-approval</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+      <c r="B10" s="3">
+        <f>LOWER($C10)</f>
+        <v/>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Can access and modify application code and integrations.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>agent-009</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>sophie</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>crm-data-sync</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>procurement</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>archive-request</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>LOWER($C11)</f>
+        <v/>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Quality Assurance</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Responsible for testing new features and reporting bugs.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>agent-010</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>calendar-integration</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>customer-feedback-collection</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="B12" s="3">
+        <f>LOWER($C12)</f>
+        <v/>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Human Resources</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Manages employee records and recruitment processes.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>agent-011</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>liam</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>survey-data-pipeline</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>legal-compliance-check</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>LOWER($C13)</f>
+        <v/>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Finance Officer</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Handles billing, invoices, and financial reports.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>agent-012</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>jade</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>task-management-sync</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>public-relations</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>assign-task-to-team, some-new-task</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B14" s="3">
+        <f>LOWER($C14)</f>
+        <v/>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Temporary Access</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Limited access for temporary users or external collaborators.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>agent-013</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>mila</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>cloud-storage-sync</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>team-lead-review</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+      <c r="B15" s="3">
+        <f>LOWER($C15)</f>
+        <v/>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Training Specialist</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Creates and delivers training materials to users.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>agent-014</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>noah</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>email-notification-pipeline</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>facilities-management</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>generate-report</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="B16" s="3">
+        <f>LOWER($C16)</f>
+        <v/>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>System Owner</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Ultimate authority over the system, can assign or revoke any role.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>agent-015</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>ella</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>survey-data-export</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>training-and-development</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>close-workflow</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DepartmentId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>human-resources</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>SUBSTITUTE(LOWER($D2), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>HR Department</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Human Resources</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>SUBSTITUTE(LOWER($D3), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Finance Department</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>information-technology</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>SUBSTITUTE(LOWER($D4), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>IT Department</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>marketing</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>SUBSTITUTE(LOWER($D5), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Department</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>SUBSTITUTE(LOWER($D6), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Sales Department</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>customer-service</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>SUBSTITUTE(LOWER($D7), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Customer Service Department</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Customer Service</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>research-and-development</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>SUBSTITUTE(LOWER($D8), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>R&amp;D Department</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Research and Development</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>legal</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>SUBSTITUTE(LOWER($D9), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Legal Department</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>procurement</t>
+        </is>
+      </c>
+      <c r="B10" s="3">
+        <f>SUBSTITUTE(LOWER($D10), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Department</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>SUBSTITUTE(LOWER($D11), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Operations Department</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
+      <c r="B12" s="3">
+        <f>SUBSTITUTE(LOWER($D12), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Administration Department</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>public-relations</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>SUBSTITUTE(LOWER($D13), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>PR Department</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Public Relations</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance</t>
+        </is>
+      </c>
+      <c r="B14" s="3">
+        <f>SUBSTITUTE(LOWER($D14), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>QA Department</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Quality Assurance</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>facilities-management</t>
+        </is>
+      </c>
+      <c r="B15" s="3">
+        <f>SUBSTITUTE(LOWER($D15), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Facilities Department</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Facilities Management</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>training-and-development</t>
+        </is>
+      </c>
+      <c r="B16" s="3">
+        <f>SUBSTITUTE(LOWER($D16), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Training Department</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Training and Development</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>HumanAgentId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Mbox</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>agent-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>agent_001</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Alice Johnson</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>alice.johnson@example.com</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>agent-002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>agent_002</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Brian Smith</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>brian.smith@example.com</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>agent-003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>agent_003</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Catherine Lee</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>catherine.lee@example.com</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>agent-004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>agent_004</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>David Kim</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>david.kim@example.com</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>agent-005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>agent_005</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Emily Chen</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>emily.chen@example.com</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>agent-006</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>agent_006</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Frank Miller</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>frank.miller@example.com</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>agent-007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>agent_007</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Grace Park</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>grace.park@example.com</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>agent-008</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>agent_008</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Henry Adams</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>henry.adams@example.com</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>agent-009</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>agent_009</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Isabella Martinez</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>isabella.martinez@example.com</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>agent-010</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>agent_010</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Jack Wilson</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>jack.wilson@example.com</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>agent-011</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>agent_011</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Karen Patel</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>karen.patel@example.com</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>agent-012</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>agent_012</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Liam Nguyen</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>liam.nguyen@example.com</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>agent-013</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>agent_013</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Monica Rivera</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>monica.rivera@example.com</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>agent-014</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>agent_014</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Nathan Brown</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>nathan.brown@example.com</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>agent-015</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>agent_015</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Olivia Clark</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>olivia.clark@example.com</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CustomerId</t>
+          <t>AIAgentId</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>EmailAddress</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>FirstName</t>
+          <t>DisplayName</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>LastName</t>
+          <t>ModelVersion</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>FullName</t>
+          <t>Roles</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>cust0001</t>
+          <t>ava</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>CUST0001</t>
+          <t>Ava</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>jane.smith@email.com</t>
+          <t>CustomerSupportBot</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Ava</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Smith</t>
-        </is>
-      </c>
-      <c r="F2" s="3">
-        <f>$E2 &amp; ", " &amp; $D2</f>
-        <v/>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>cust0002</t>
+          <t>leo</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CUST0002</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>john.doe@email.com</t>
+          <t>SalesAssistantAI</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Doe</t>
-        </is>
-      </c>
-      <c r="F3" s="3">
-        <f>$E3 &amp; ", " &amp; $D3</f>
-        <v/>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>cust0003</t>
+          <t>maya</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CUST0003</t>
+          <t>Maya</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>emily.jones@email.com</t>
+          <t>HRRecruiterBot</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Maya</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jones</t>
-        </is>
-      </c>
-      <c r="F4" s="3">
-        <f>$E4 &amp; ", " &amp; $D4</f>
-        <v/>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Eli</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>FinanceAdvisorAI</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Eli</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>zara</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Zara</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>MarketingCopyAI</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Zara</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>owen</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Owen</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>LegalDraftBot</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Owen</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>nina</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>MedicalAssistantAI</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>kai</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Kai</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>TravelPlannerBot</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Kai</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>sophie</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Sophie</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>EcommerceHelperAI</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Sophie</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>EducationTutorBot</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>liam</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Liam</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>RealEstateAdvisorAI</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Liam</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>jade</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Jade</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>FitnessCoachBot</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Jade</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>mila</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Mila</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>EventPlannerAI</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Mila</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>noah</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Noah</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>PersonalFinanceBot</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Noah</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ella</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Ella</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>ContentEditorAI</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Ella</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>AutomatedPipelineId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>lead-notification-pipeline</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>lead-notification-pipeline</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Salesforce to Slack Lead Alert</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Lead Notification Pipeline</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>e-commerce-order-sync</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>e-commerce-order-sync</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Shopify Order to QuickBooks Invoice</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>E-commerce Order Sync</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>issue-tracking-bridge</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>issue-tracking-bridge</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Jira Issue to Trello Card</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Issue Tracking Bridge</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>newsletter-signup-sync</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>newsletter-signup-sync</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Google Sheets to Mailchimp Subscriber</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Newsletter Signup Sync</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>support-ticket-automation</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>support-ticket-automation</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Zendesk Ticket to Asana Task</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Support Ticket Automation</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>devops-integration</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>devops-integration</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>GitHub PR to Jira Story</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>DevOps Integration</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>finance-automation</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>finance-automation</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Stripe Payment to Xero Invoice</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Finance Automation</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>project-intake-pipeline</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>project-intake-pipeline</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Airtable Form to Monday.com Item</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Project Intake Pipeline</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>crm-data-sync</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>crm-data-sync</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>HubSpot Contact to Salesforce Lead</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>CRM Data Sync</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>calendar-integration</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>calendar-integration</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Google Calendar Event to Teams Meeting</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Calendar Integration</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>survey-data-pipeline</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>survey-data-pipeline</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Typeform Response to Notion Database</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Survey Data Pipeline</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>task-management-sync</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>task-management-sync</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Trello Card to Google Tasks</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Task Management Sync</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>cloud-storage-sync</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>cloud-storage-sync</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Dropbox Upload to Google Drive</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Storage Sync</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>email-notification-pipeline</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>email-notification-pipeline</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Outlook Email to Slack Channel</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Email Notification Pipeline</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>survey-data-export</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>survey-data-export</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>SurveyMonkey Response to Excel Sheet</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Survey Data Export</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/execution-substrates/xlsx/rulebook.xlsx
+++ b/execution-substrates/xlsx/rulebook.xlsx
@@ -7,7 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Customers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Workflows" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="WorkflowSteps" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ApprovalGates" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="PrecedesSteps" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Roles" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Departments" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="HumanAgents" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="AIAgents" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="AutomatedPipelines" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -159,27 +167,252 @@
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Identifier for the customers.</t>
+        <t>Short machine-friendly name for the workflow. Used for programmatic reference and URL slug generation.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Human-readable title of the workflow. Maps to dct:title from Dublin Core. Example: 'Production Deployment Workflow', 'Employee Onboarding'.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Detailed description of the workflow's purpose and scope. Maps to dct:description from Dublin Core. Should explain what business goal the workflow achieves.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>External system identifier for cross-referencing. Maps to dct:identifier from Dublin Core. This is the join key back to document management systems, ticket systems, or other operational systems.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Last modification timestamp. Maps to dct:modified from Dublin Core. Critical for answering CQ5: 'Which workflows haven't been reviewed or updated in twelve months?'</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Reference to workflow steps. Represents the ntwf:hasStep relationship linking workflows to their constituent steps.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Calculated count of workflow steps in this workflow. Useful for workflow complexity analysis and reporting.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ERB Rulebook</author>
+  </authors>
+  <commentList>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Foreign key to the parent workflow. Represents the inverse of ntwf:hasStep, enabling navigation from step to its containing workflow (ntwf:isStepOf).</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Integer ordinal position of the step within its workflow. Maps to ntwf:sequencePosition, declared as owl:FunctionalProperty (each step has exactly one position). Enables positional queries.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Foreign key to the Role responsible for executing this step. Maps to ntwf:assignedRole. Critical for implementing Heuristic 2 (role-agent separation): steps point to roles, not directly to agents.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Boolean flag indicating whether a human agent must fill the assigned role. Maps to ntwf:requiresHumanApproval. Enables answering CQ3: 'Which steps require human decisions vs. AI execution?'</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Foreign key to ApprovalGate if this step is a decision checkpoint. When populated, indicates this step blocks workflow execution until explicit authorization is given.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Reference to steps that must complete before this step can execute. Part of the ntwf:precedesStep transitive ordering relationship.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ERB Rulebook</author>
+  </authors>
+  <commentList>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Back-reference to workflow steps that use this approval gate. Enables finding all steps requiring this specific gate.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Integer number of hours that may elapse on a pending gate before the ntwf:delegatesTo chain activates. Maps to ntwf:escalationThresholdHours. Domain applies only to ApprovalGate individuals.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ERB Rulebook</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Ordinal sequence number for the relationship. Used for sorting and display.</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Thec ustomers email address</t>
+        <t>Foreign key to the step that comes BEFORE. The source of the 'precedes' relationship.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ERB Rulebook</author>
+  </authors>
+  <commentList>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Human-readable display name. Maps to rdfs:label. Per Heuristic 6: if you cannot write a clear label, you do not yet understand the concept well enough to model it.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Detailed description of the role's responsibilities and scope. Maps to rdfs:comment. Should define what the role covers, what it excludes, and how it differs from adjacent roles.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Foreign key to the Department that owns this role. Maps to ntwf:ownedBy (owl:FunctionalProperty). Enables answering CQ7: 'Which workflows involve both Engineering and Legal?'</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Foreign key to the fallback Role in an escalation chain. Maps to ntwf:delegatesTo. Enables answering CQ6: 'What happens when the VP of Engineering is unavailable?'</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>Back-reference to workflow steps assigned to this role. Inverse of WorkflowSteps.AssignedRole.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ERB Rulebook</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Human-readable display name of the department. Should match organizational terminology for stakeholder communication.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Human-readable display name of the department. Should match organizational terminology for stakeholder communication.</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>First Name of the customer - used to make the full name</t>
+        <t>Machine-friendly name for programmatic reference.</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>Last Name of the customer - used to make the full name</t>
+        <t>Back-reference to roles owned by this department. Inverse of Roles.OwnedBy.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ERB Rulebook</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Full name of the person. Maps to foaf:name. Note: FOAF's name property is appropriate for persons, not for software systems (which use schema:name).</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Email address of the person. Maps to foaf:mbox. Used for notifications and organizational directory integration.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Back-reference to roles currently filled by this agent. Inverse of Roles.FilledBy_HumanAgent.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ERB Rulebook</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Display name of the AI agent. Maps to schema:name (not foaf:name, which is for persons).</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Version string of the AI model. Maps to ntwf:modelVersion. Makes AI-produced artifacts auditable at the version level. The domain declaration means this property applies only to AIAgent individuals.</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>Full name is computed from the first and last name of the customer</t>
+        <t>Back-reference to roles currently filled by this AI agent. Inverse of Roles.FilledBy_AIAgent.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ERB Rulebook</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Display name of the pipeline. Maps to schema:name (appropriate for software systems, unlike foaf:name which is for persons).</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Back-reference to roles currently filled by this pipeline. Inverse of Roles.FilledBy_AutomatedPipeline.</t>
       </text>
     </comment>
   </commentList>
@@ -475,140 +708,5303 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>WorkflowId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>WorkflowSteps</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>CountOfNonProposedSteps</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>HasMoreThan1Step</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>performance-review</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>SUBSTITUTE(LOWER($C2), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Performance Review</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Annual Performance Review</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Structured workflow for conducting annual employee performance evaluations.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>WF-PRV-007</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>system-notification-sent, step-2, recwwXHLqxKPhj6Mt</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" s="3">
+        <f>$J2 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>change-management</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>SUBSTITUTE(LOWER($C3), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Change Management</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Change Management Workflow</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Structured process for requesting, evaluating, and implementing organizational changes.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>WF-CHM-015</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-27</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>close-workflow, step1, asdf</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" s="3">
+        <f>$J3 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>incident-reporting</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>SUBSTITUTE(LOWER($C4), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Incident Reporting</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Incident Reporting Process</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Steps for reporting, investigating, and resolving workplace incidents.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>WF-INC-014</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>generate-report</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="3">
+        <f>$J4 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>customer-feedback</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>SUBSTITUTE(LOWER($C5), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Customer Feedback</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Customer Feedback Collection</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Workflow for collecting, analyzing, and acting on customer feedback.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>WF-CFB-009</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-25</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>archive-request</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="3">
+        <f>$J5 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>project-kickoff</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>SUBSTITUTE(LOWER($C6), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Project Kickoff</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Project Kickoff Process</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Steps to initiate a new project, including team assignment and goal setting.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>WF-PKO-010</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-20</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>customer-feedback-collection</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="3">
+        <f>$J6 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>onboarding</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>SUBSTITUTE(LOWER($C7), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Employee Onboarding</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>A step-by-step process to onboard new employees, including document collection, orientation, and training.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>WF-ONB-001</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>submit-request</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="3">
+        <f>$J7 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>content-publishing</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>SUBSTITUTE(LOWER($C8), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Content Publishing</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Content Publishing Process</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Workflow for drafting, reviewing, and publishing content to the company website.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>WF-CNT-003</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>automated-eligibility-check</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="3">
+        <f>$J8 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>expense-reimbursement</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>SUBSTITUTE(LOWER($C9), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Expense Reimbursement</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Expense Reimbursement Process</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Steps for employees to submit expenses and receive reimbursements after approval.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>WF-EXP-006</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance-review</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="3">
+        <f>$J9 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>procurement</t>
+        </is>
+      </c>
+      <c r="B10" s="3">
+        <f>SUBSTITUTE(LOWER($C10), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Workflow</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Process for requesting, approving, and purchasing goods or services.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>WF-PRC-008</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-02</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>final-approval</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="3">
+        <f>$J10 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>invoice-approval</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>SUBSTITUTE(LOWER($C11), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Approval</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Approval Workflow</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Automated workflow for reviewing, approving, and processing vendor invoices.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>WF-INV-002</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>manager-review</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="3">
+        <f>$J11 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>asset-management</t>
+        </is>
+      </c>
+      <c r="B12" s="3">
+        <f>SUBSTITUTE(LOWER($C12), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Asset Management</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Asset Management Process</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Process for tracking, maintaining, and auditing company assets.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>WF-ASM-012</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>assign-task-to-team</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="3">
+        <f>$J12 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>contract-review</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>SUBSTITUTE(LOWER($C13), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Contract Review</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Contract Review Workflow</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Workflow for legal and management review of contracts before signing.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>WF-CTR-011</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>legal-compliance-check</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="3">
+        <f>$J13 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="B14" s="3">
+        <f>SUBSTITUTE(LOWER($C14), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Recruitment</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Recruitment Workflow</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Workflow for posting jobs, screening candidates, and scheduling interviews.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>WF-RCT-013</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>team-lead-review</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="3">
+        <f>$J14 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>it-support</t>
+        </is>
+      </c>
+      <c r="B15" s="3">
+        <f>SUBSTITUTE(LOWER($C15), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>IT Support</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>IT Support Ticketing</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Workflow for submitting, triaging, and resolving IT support tickets.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>WF-ITS-005</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>document-verification</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="3">
+        <f>$J15 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>leave-request</t>
+        </is>
+      </c>
+      <c r="B16" s="3">
+        <f>SUBSTITUTE(LOWER($C16), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Leave Request</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Leave Request Workflow</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Process for employees to submit, review, and approve leave requests.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>WF-LRQ-004</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="3">
+        <f>$J16 &gt; 1</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>WorkflowStepId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Workflow</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>SequencePosition</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>AssignedRole</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>RequiresHumanApproval</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ApprovalGate</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>PrecededBySteps</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>submit-request</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>SUBSTITUTE(LOWER($C2), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Submit Request</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>onboarding</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>initial-review</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>step-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>manager-review</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>SUBSTITUTE(LOWER($C3), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Manager Review</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>invoice-approval</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>manager-approval</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>step-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>recwwXHLqxKPhj6Mt</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>SUBSTITUTE(LOWER($C4), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>performance-review</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>automated-eligibility-check</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>SUBSTITUTE(LOWER($C5), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Automated Eligibility Check</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>content-publishing</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>it-security-gate</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>step-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>SUBSTITUTE(LOWER($C6), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Finance Approval</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>leave-request</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>step-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>document-verification</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>SUBSTITUTE(LOWER($C7), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Document Verification</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>it-support</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>compliance-check</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>step-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance-review</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>SUBSTITUTE(LOWER($C8), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Quality Assurance Review</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>expense-reimbursement</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>step-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>system-notification-sent</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>SUBSTITUTE(LOWER($C9), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>System Notification Sent</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>performance-review</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>final-authorization</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>step-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>final-approval</t>
+        </is>
+      </c>
+      <c r="B10" s="3">
+        <f>SUBSTITUTE(LOWER($C10), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Final Approval</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>procurement</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>manager-approval</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>step-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>archive-request</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>SUBSTITUTE(LOWER($C11), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Archive Request</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>customer-feedback</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>it-security-gate</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>step-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>customer-feedback-collection</t>
+        </is>
+      </c>
+      <c r="B12" s="3">
+        <f>SUBSTITUTE(LOWER($C12), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Customer Feedback Collection</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>project-kickoff</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>customer-confirmation</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>step-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>legal-compliance-check</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>SUBSTITUTE(LOWER($C13), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Legal Compliance Check</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>contract-review</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>legal-review</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>step-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>assign-task-to-team</t>
+        </is>
+      </c>
+      <c r="B14" s="3">
+        <f>SUBSTITUTE(LOWER($C14), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Assign Task to Team</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>asset-management</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>executive-sign-off</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>step-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>some-new-task</t>
+        </is>
+      </c>
+      <c r="B15" s="3">
+        <f>SUBSTITUTE(LOWER($C15), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Some new task</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>some-new-gate</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>assign-task-to-team</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>team-lead-review</t>
+        </is>
+      </c>
+      <c r="B16" s="3">
+        <f>SUBSTITUTE(LOWER($C16), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Team Lead Review</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>legal-review</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>step-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>generate-report</t>
+        </is>
+      </c>
+      <c r="B17" s="3">
+        <f>SUBSTITUTE(LOWER($C17), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Generate Report</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>incident-reporting</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>step-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>close-workflow</t>
+        </is>
+      </c>
+      <c r="B18" s="3">
+        <f>SUBSTITUTE(LOWER($C18), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Close Workflow</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>change-management</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>executive-sign-off</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>step-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>step1</t>
+        </is>
+      </c>
+      <c r="B19" s="3">
+        <f>SUBSTITUTE(LOWER($C19), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>step1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>change-management</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>asdf</t>
+        </is>
+      </c>
+      <c r="B20" s="3">
+        <f>SUBSTITUTE(LOWER($C20), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>asdf</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>change-management</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>step-2</t>
+        </is>
+      </c>
+      <c r="B21" s="3">
+        <f>SUBSTITUTE(LOWER($C21), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Step 2</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>performance-review</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ApprovalGateId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>WorkflowSteps</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>EscalationThresholdHours</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>initial-review</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>SUBSTITUTE(LOWER($C2), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Initial Review</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>submit-request</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>manager-approval</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>SUBSTITUTE(LOWER($C3), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Manager Approval</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>final-approval, manager-review</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>compliance-check</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>SUBSTITUTE(LOWER($C4), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Compliance Check</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>document-verification</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>final-authorization</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>SUBSTITUTE(LOWER($C5), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Final Authorization</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>system-notification-sent</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>executive-sign-off</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>SUBSTITUTE(LOWER($C6), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Executive Sign-off</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>close-workflow, assign-task-to-team</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>SUBSTITUTE(LOWER($C7), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Quality Assurance</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance-review</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>legal-review</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>SUBSTITUTE(LOWER($C8), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Legal Review</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>team-lead-review, legal-compliance-check</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>SUBSTITUTE(LOWER($C9), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Finance Approval</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>generate-report, finance-approval</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>it-security-gate</t>
+        </is>
+      </c>
+      <c r="B10" s="3">
+        <f>SUBSTITUTE(LOWER($C10), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>IT Security Gate</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>archive-request, automated-eligibility-check</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>customer-confirmation</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>SUBSTITUTE(LOWER($C11), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Customer Confirmation</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>customer-feedback-collection</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>some-new-gate</t>
+        </is>
+      </c>
+      <c r="B12" s="3">
+        <f>SUBSTITUTE(LOWER($C12), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>some new gate</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>some-new-task</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PrecedesStepId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>WorkflowStep</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>StepNumber</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>step-1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>step-1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>submit-request</t>
+        </is>
+      </c>
+      <c r="D2" s="3">
+        <f>"Step-" &amp; $E2</f>
+        <v/>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>step-2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>step-2</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>manager-review</t>
+        </is>
+      </c>
+      <c r="D3" s="3">
+        <f>"Step-" &amp; $E3</f>
+        <v/>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>step-3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>step-3</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>automated-eligibility-check</t>
+        </is>
+      </c>
+      <c r="D4" s="3">
+        <f>"Step-" &amp; $E4</f>
+        <v/>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>step-4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>step-4</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="D5" s="3">
+        <f>"Step-" &amp; $E5</f>
+        <v/>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>step-5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>step-5</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>document-verification</t>
+        </is>
+      </c>
+      <c r="D6" s="3">
+        <f>"Step-" &amp; $E6</f>
+        <v/>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>step-6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>step-6</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance-review</t>
+        </is>
+      </c>
+      <c r="D7" s="3">
+        <f>"Step-" &amp; $E7</f>
+        <v/>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>step-7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>step-7</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>system-notification-sent</t>
+        </is>
+      </c>
+      <c r="D8" s="3">
+        <f>"Step-" &amp; $E8</f>
+        <v/>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>step-8</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>step-8</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>final-approval</t>
+        </is>
+      </c>
+      <c r="D9" s="3">
+        <f>"Step-" &amp; $E9</f>
+        <v/>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>step-9</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>step-9</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>archive-request</t>
+        </is>
+      </c>
+      <c r="D10" s="3">
+        <f>"Step-" &amp; $E10</f>
+        <v/>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>step-10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>step-10</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>customer-feedback-collection</t>
+        </is>
+      </c>
+      <c r="D11" s="3">
+        <f>"Step-" &amp; $E11</f>
+        <v/>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>step-11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>step-11</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>legal-compliance-check</t>
+        </is>
+      </c>
+      <c r="D12" s="3">
+        <f>"Step-" &amp; $E12</f>
+        <v/>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>step-12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>step-12</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>assign-task-to-team</t>
+        </is>
+      </c>
+      <c r="D13" s="3">
+        <f>"Step-" &amp; $E13</f>
+        <v/>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>step-13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>step-13</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>team-lead-review</t>
+        </is>
+      </c>
+      <c r="D14" s="3">
+        <f>"Step-" &amp; $E14</f>
+        <v/>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>step-14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>step-14</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>generate-report</t>
+        </is>
+      </c>
+      <c r="D15" s="3">
+        <f>"Step-" &amp; $E15</f>
+        <v/>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>step-15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>step-15</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>close-workflow</t>
+        </is>
+      </c>
+      <c r="D16" s="3">
+        <f>"Step-" &amp; $E16</f>
+        <v/>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>assign-task-to-team</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>assign-task-to-team</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>some-new-task</t>
+        </is>
+      </c>
+      <c r="D17" s="3">
+        <f>"Step-" &amp; $E17</f>
+        <v/>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>RoleId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>FilledByHumanAgent</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>FilledByAIAgent</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>FilledByAutomatedPipeline</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>OwnedBy</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>DelegatesTo</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WorkflowSteps</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>FromDelegatesTo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>LOWER($C2)</f>
+        <v/>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Has full access to all system features and settings.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>agent-001</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>ava</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>lead-notification-pipeline</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>human-resources</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>submit-request</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>LOWER($C3)</f>
+        <v/>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Editor</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Content Editor</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Can create, edit, and delete content but cannot change system settings.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>agent-002</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>leo</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>e-commerce-order-sync</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>manager-review</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>LOWER($C4)</f>
+        <v/>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Viewer</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Read-Only</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Can view content but cannot make any changes.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>agent-003</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>maya</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>issue-tracking-bridge</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>information-technology</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>automated-eligibility-check</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>LOWER($C5)</f>
+        <v/>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Moderator</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Forum Moderator</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Can manage user comments and moderate discussions.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>agent-004</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>newsletter-signup-sync</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>marketing</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>LOWER($C6)</f>
+        <v/>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Contributor</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Content Contributor</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Can submit new content for review but cannot publish directly.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>agent-005</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>zara</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>support-ticket-automation</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>document-verification</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>LOWER($C7)</f>
+        <v/>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Oversees project progress and manages team assignments.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>agent-006</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>owen</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>devops-integration</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>customer-service</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance-review</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>LOWER($C8)</f>
+        <v/>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Customer Support</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Handles user inquiries and provides technical assistance.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>agent-007</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>nina</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>finance-automation</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>research-and-development</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>system-notification-sent</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>LOWER($C9)</f>
+        <v/>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Has access to analytics and reporting tools.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>agent-008</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>kai</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>project-intake-pipeline</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>legal</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>final-approval</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+      <c r="B10" s="3">
+        <f>LOWER($C10)</f>
+        <v/>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Can access and modify application code and integrations.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>agent-009</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>sophie</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>crm-data-sync</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>procurement</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>archive-request</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>LOWER($C11)</f>
+        <v/>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Quality Assurance</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Responsible for testing new features and reporting bugs.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>agent-010</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>calendar-integration</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>customer-feedback-collection</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="B12" s="3">
+        <f>LOWER($C12)</f>
+        <v/>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Human Resources</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Manages employee records and recruitment processes.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>agent-011</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>liam</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>survey-data-pipeline</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>legal-compliance-check</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>LOWER($C13)</f>
+        <v/>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Finance Officer</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Handles billing, invoices, and financial reports.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>agent-012</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>jade</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>task-management-sync</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>public-relations</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>assign-task-to-team, some-new-task</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B14" s="3">
+        <f>LOWER($C14)</f>
+        <v/>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Temporary Access</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Limited access for temporary users or external collaborators.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>agent-013</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>mila</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>cloud-storage-sync</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>team-lead-review</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+      <c r="B15" s="3">
+        <f>LOWER($C15)</f>
+        <v/>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Training Specialist</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Creates and delivers training materials to users.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>agent-014</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>noah</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>email-notification-pipeline</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>facilities-management</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>generate-report</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="B16" s="3">
+        <f>LOWER($C16)</f>
+        <v/>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>System Owner</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Ultimate authority over the system, can assign or revoke any role.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>agent-015</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>ella</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>survey-data-export</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>training-and-development</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>close-workflow</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DepartmentId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>human-resources</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>SUBSTITUTE(LOWER($D2), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>HR Department</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Human Resources</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>SUBSTITUTE(LOWER($D3), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Finance Department</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>information-technology</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>SUBSTITUTE(LOWER($D4), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>IT Department</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>marketing</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>SUBSTITUTE(LOWER($D5), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Department</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>SUBSTITUTE(LOWER($D6), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Sales Department</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>customer-service</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>SUBSTITUTE(LOWER($D7), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Customer Service Department</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Customer Service</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>research-and-development</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>SUBSTITUTE(LOWER($D8), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>R&amp;D Department</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Research and Development</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>legal</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>SUBSTITUTE(LOWER($D9), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Legal Department</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>procurement</t>
+        </is>
+      </c>
+      <c r="B10" s="3">
+        <f>SUBSTITUTE(LOWER($D10), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Department</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>SUBSTITUTE(LOWER($D11), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Operations Department</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
+      <c r="B12" s="3">
+        <f>SUBSTITUTE(LOWER($D12), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Administration Department</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>public-relations</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>SUBSTITUTE(LOWER($D13), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>PR Department</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Public Relations</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance</t>
+        </is>
+      </c>
+      <c r="B14" s="3">
+        <f>SUBSTITUTE(LOWER($D14), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>QA Department</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Quality Assurance</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>facilities-management</t>
+        </is>
+      </c>
+      <c r="B15" s="3">
+        <f>SUBSTITUTE(LOWER($D15), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Facilities Department</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Facilities Management</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>training-and-development</t>
+        </is>
+      </c>
+      <c r="B16" s="3">
+        <f>SUBSTITUTE(LOWER($D16), " ", "-")</f>
+        <v/>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Training Department</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Training and Development</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>HumanAgentId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Mbox</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>agent-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>agent_001</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Alice Johnson</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>alice.johnson@example.com</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>agent-002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>agent_002</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Brian Smith</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>brian.smith@example.com</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>agent-003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>agent_003</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Catherine Lee</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>catherine.lee@example.com</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>agent-004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>agent_004</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>David Kim</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>david.kim@example.com</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>agent-005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>agent_005</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Emily Chen</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>emily.chen@example.com</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>agent-006</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>agent_006</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Frank Miller</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>frank.miller@example.com</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>agent-007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>agent_007</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Grace Park</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>grace.park@example.com</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>agent-008</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>agent_008</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Henry Adams</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>henry.adams@example.com</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>agent-009</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>agent_009</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Isabella Martinez</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>isabella.martinez@example.com</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>agent-010</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>agent_010</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Jack Wilson</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>jack.wilson@example.com</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>agent-011</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>agent_011</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Karen Patel</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>karen.patel@example.com</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>agent-012</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>agent_012</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Liam Nguyen</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>liam.nguyen@example.com</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>agent-013</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>agent_013</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Monica Rivera</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>monica.rivera@example.com</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>agent-014</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>agent_014</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Nathan Brown</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>nathan.brown@example.com</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>agent-015</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>agent_015</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Olivia Clark</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>olivia.clark@example.com</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CustomerId</t>
+          <t>AIAgentId</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>EmailAddress</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>FirstName</t>
+          <t>DisplayName</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>LastName</t>
+          <t>ModelVersion</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>FullName</t>
+          <t>Roles</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>cust0001</t>
+          <t>ava</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>CUST0001</t>
+          <t>Ava</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>jane.smith@email.com</t>
+          <t>CustomerSupportBot</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Ava</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Smith</t>
-        </is>
-      </c>
-      <c r="F2" s="3">
-        <f>$D2 &amp; " " &amp; $E2</f>
-        <v/>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>cust0002</t>
+          <t>leo</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CUST0002</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>john.doe@email.com</t>
+          <t>SalesAssistantAI</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Doe</t>
-        </is>
-      </c>
-      <c r="F3" s="3">
-        <f>$D3 &amp; " " &amp; $E3</f>
-        <v/>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>cust0003</t>
+          <t>maya</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CUST0003</t>
+          <t>Maya</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>emily.jones@email.com</t>
+          <t>HRRecruiterBot</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Maya</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jones</t>
-        </is>
-      </c>
-      <c r="F4" s="3">
-        <f>$D4 &amp; " " &amp; $E4</f>
-        <v/>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Eli</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>FinanceAdvisorAI</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Eli</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>zara</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Zara</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>MarketingCopyAI</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Zara</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>owen</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Owen</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>LegalDraftBot</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Owen</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>nina</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>MedicalAssistantAI</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>kai</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Kai</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>TravelPlannerBot</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Kai</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>sophie</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Sophie</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>EcommerceHelperAI</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Sophie</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>EducationTutorBot</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>liam</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Liam</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>RealEstateAdvisorAI</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Liam</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>jade</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Jade</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>FitnessCoachBot</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Jade</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>mila</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Mila</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>EventPlannerAI</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Mila</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>noah</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Noah</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>PersonalFinanceBot</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Noah</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ella</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Ella</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>ContentEditorAI</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Ella</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>AutomatedPipelineId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>lead-notification-pipeline</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>lead-notification-pipeline</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Salesforce to Slack Lead Alert</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Lead Notification Pipeline</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>e-commerce-order-sync</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>e-commerce-order-sync</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Shopify Order to QuickBooks Invoice</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>E-commerce Order Sync</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>issue-tracking-bridge</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>issue-tracking-bridge</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Jira Issue to Trello Card</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Issue Tracking Bridge</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>newsletter-signup-sync</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>newsletter-signup-sync</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Google Sheets to Mailchimp Subscriber</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Newsletter Signup Sync</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>support-ticket-automation</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>support-ticket-automation</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Zendesk Ticket to Asana Task</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Support Ticket Automation</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>devops-integration</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>devops-integration</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>GitHub PR to Jira Story</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>DevOps Integration</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>finance-automation</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>finance-automation</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Stripe Payment to Xero Invoice</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Finance Automation</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>project-intake-pipeline</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>project-intake-pipeline</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Airtable Form to Monday.com Item</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Project Intake Pipeline</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>crm-data-sync</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>crm-data-sync</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>HubSpot Contact to Salesforce Lead</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>CRM Data Sync</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>calendar-integration</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>calendar-integration</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Google Calendar Event to Teams Meeting</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Calendar Integration</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>survey-data-pipeline</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>survey-data-pipeline</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Typeform Response to Notion Database</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Survey Data Pipeline</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>task-management-sync</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>task-management-sync</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Trello Card to Google Tasks</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Task Management Sync</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>cloud-storage-sync</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>cloud-storage-sync</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Dropbox Upload to Google Drive</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Storage Sync</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>email-notification-pipeline</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>email-notification-pipeline</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Outlook Email to Slack Channel</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Email Notification Pipeline</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>survey-data-export</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>survey-data-export</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>SurveyMonkey Response to Excel Sheet</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Survey Data Export</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/execution-substrates/xlsx/rulebook.xlsx
+++ b/execution-substrates/xlsx/rulebook.xlsx
@@ -145,6 +145,191 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ERB Rulebook</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Human-readable name for the workflow. Maps to dct:title per Dublin Core.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Detailed description of the workflow purpose and scope. Maps to dct:description per Dublin Core.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Date the workflow was created. Maps to dct:created per Dublin Core.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Date the workflow was last modified. Maps to dct:modified. Used to identify stale workflows per NTWF CQ5.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>External reference identifier (e.g., ticket number). Maps to dct:identifier. Join key to operational systems.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Steps contained in this workflow. Inverse of IsStepOf. Maps to ntwf:hasStep.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Count of steps in this workflow. Aggregation over IsStepOf relationship.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ERB Rulebook</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Human-readable name for the step. Maps to rdfs:label.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Ordinal position in workflow sequence. Maps to ntwf:sequencePosition (functional). Supports positional ordering queries.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Whether this step requires a human agent. Maps to ntwf:requiresHumanApproval. Answers NTWF CQ3.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Parent workflow containing this step. Inverse of WorkflowSteps. Maps to ntwf:isStepOf.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Role responsible for this step. Maps to ntwf:assignedRole (functional). Implements role-agent separation.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Denormalized lookup of parent workflow title.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Denormalized lookup of parent workflow description.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Denormalized lookup of parent workflow external identifier.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Denormalized lookup of assigned role label.</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>Denormalized lookup of assigned role comment/description.</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Denormalized lookup of agent currently filling the assigned role.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ERB Rulebook</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Human-readable name for the role. Maps to rdfs:label.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Description of the role's responsibilities. Maps to rdfs:comment.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Agent currently filling this role. Maps to ntwf:filledBy. The change-management triple - update this when personnel change.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Steps assigned to this role. Inverse of AssignedRole.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Count of workflow steps assigned to this role.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Denormalized lookup of agent name (foaf:name) filling this role.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Denormalized lookup of agent email (foaf:mbox) filling this role.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ERB Rulebook</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Full name of the person. Maps to foaf:name per FOAF ontology.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Email address of the person. Maps to foaf:mbox per FOAF ontology. Used for contact and identity resolution.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Roles filled by this agent. Inverse of FilledBy.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Count of roles currently filled by this agent.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -533,6 +718,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -789,6 +975,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -951,6 +1138,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -960,14 +1148,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,7 +1181,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>CountOfRles</t>
+          <t>CountOfRoles</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1213,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>james-okafor</t>
+          <t>maria-gonzalez</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>James Okafor</t>
+          <t>Maria Gonzalez</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>james.okafor@specialsolutions.example</t>
+          <t>maria.gonzalez@specialsolutions.example</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
@@ -1043,7 +1231,155 @@
         <v>0</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>james-okafor</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>James Okafor</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>james.okafor@specialsolutions.example</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>maria-gonzalez</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Maria Gonzalez</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>maria.gonzalez@specialsolutions.example</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>james-okafor</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>James Okafor</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>james.okafor@specialsolutions.example</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>maria-gonzalez</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Maria Gonzalez</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>maria.gonzalez@specialsolutions.example</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>james-okafor</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>James Okafor</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>james.okafor@specialsolutions.example</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>maria-gonzalez</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Maria Gonzalez</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>maria.gonzalez@specialsolutions.example</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>james-okafor</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>James Okafor</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>james.okafor@specialsolutions.example</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/execution-substrates/xlsx/rulebook.xlsx
+++ b/execution-substrates/xlsx/rulebook.xlsx
@@ -296,6 +296,11 @@
     <comment ref="H1" authorId="0" shapeId="0">
       <text>
         <t>Denormalized lookup of agent email (foaf:mbox) filling this role.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Role to escalate to when this role's agent is unavailable. Maps to ntwf:delegatesTo. Enables delegation chain queries.</t>
       </text>
     </comment>
   </commentList>
@@ -985,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -996,6 +1001,7 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1039,6 +1045,11 @@
           <t>FilledByMBox</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>DelegatesTo</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1079,6 +1090,7 @@
           <t>maria.gonzalez@specialsolutions.example</t>
         </is>
       </c>
+      <c r="I2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1107,6 +1119,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1135,6 +1148,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1148,7 +1162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1213,168 +1227,21 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>maria-gonzalez</t>
+          <t>james-okafor</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Maria Gonzalez</t>
+          <t>James Okafor</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>maria.gonzalez@specialsolutions.example</t>
+          <t>james.okafor@specialsolutions.example</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>james-okafor</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>James Okafor</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>james.okafor@specialsolutions.example</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>maria-gonzalez</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Maria Gonzalez</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>maria.gonzalez@specialsolutions.example</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>james-okafor</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>James Okafor</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>james.okafor@specialsolutions.example</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>maria-gonzalez</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Maria Gonzalez</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>maria.gonzalez@specialsolutions.example</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>james-okafor</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>James Okafor</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>james.okafor@specialsolutions.example</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>maria-gonzalez</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Maria Gonzalez</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>maria.gonzalez@specialsolutions.example</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>james-okafor</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>James Okafor</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>james.okafor@specialsolutions.example</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="n">
         <v>0</v>
       </c>
     </row>

--- a/execution-substrates/xlsx/rulebook.xlsx
+++ b/execution-substrates/xlsx/rulebook.xlsx
@@ -290,17 +290,17 @@
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
+        <t>Role to escalate to when this role's agent is unavailable. Maps to ntwf:delegatesTo. Enables delegation chain queries.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
         <t>Denormalized lookup of agent name (foaf:name) filling this role.</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <t>Denormalized lookup of agent email (foaf:mbox) filling this role.</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t>Role to escalate to when this role's agent is unavailable. Maps to ntwf:delegatesTo. Enables delegation chain queries.</t>
       </text>
     </comment>
   </commentList>
@@ -990,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -999,9 +999,11 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1037,17 +1039,27 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>DelegatesTo</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Label_from_DelegatesTo</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>FilledByName</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>FilledByMBox</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>DelegatesTo</t>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>DelegatedToBy</t>
         </is>
       </c>
     </row>
@@ -1082,15 +1094,25 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>vp-engineering</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>VP Engineering</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
           <t>Maria Gonzalez</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>maria.gonzalez@specialsolutions.example</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1120,6 +1142,8 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1149,6 +1173,78 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>vp-engineering</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>VP Engineering</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Secondary role in delegation chain. Escalation from Release Manager when primary agent unavailable. Article CQ6.</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>cto</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>release-manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>cto</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Final role in delegation chain. Ultimate authority for release decisions. Article CQ6.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>vp-engineering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/execution-substrates/xlsx/rulebook.xlsx
+++ b/execution-substrates/xlsx/rulebook.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Jannice</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">

--- a/execution-substrates/xlsx/rulebook.xlsx
+++ b/execution-substrates/xlsx/rulebook.xlsx
@@ -7,7 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Customers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="AppUsers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Shapes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sides" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Widgets" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ERBVersions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ERBCustomizations" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="MagicLinkIntegration" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -157,29 +163,74 @@
     <author>ERB Rulebook</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0">
+    <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>Identifier for the customers.</t>
+        <t>Label for this edge</t>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
+    <comment ref="G1" authorId="0" shapeId="0">
       <text>
-        <t>Thec ustomers email address</t>
+        <t>Is this the Hypotenuse of a Right Angle Triangle?</t>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
+    <comment ref="H1" authorId="0" shapeId="0">
       <text>
-        <t>First Name of the customer - used to make the full name</t>
+        <t>Is this the Hypotenuse of a Right Angle Triangle?</t>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
+    <comment ref="I1" authorId="0" shapeId="0">
       <text>
-        <t>Last Name of the customer - used to make the full name</t>
+        <t>Invalid if it is a Triangle with Mismatchd Edge Lengths and Angles.</t>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
+    <comment ref="J1" authorId="0" shapeId="0">
       <text>
-        <t>Full name is computed from the first and last name of the customer</t>
+        <t>Does the Pythagorean Theorem Hold?</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Edge Length</t>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <t>Length</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <t>Next Edge Length</t>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Angle</t>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0" shapeId="0">
+      <text>
+        <t>Internal angles for the shapes</t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0" shapeId="0">
+      <text>
+        <t>Next Angle</t>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Edge</t>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0" shapeId="0">
+      <text>
+        <t>Next Edge</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0">
+      <text>
+        <t>Shape</t>
       </text>
     </comment>
   </commentList>
@@ -475,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -484,17 +535,18 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CustomerId</t>
+          <t>AppUserId</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -504,115 +556,2548 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>FirstName</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>LastName</t>
+          <t>IsActive</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>FullName</t>
+          <t>Widgets</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>cust0001</t>
+          <t>ej</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>CUST0001</t>
+          <t>EJ</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>jane.smith@email.com</t>
+          <t>ej@ssot.me</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Jannice</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Smith</t>
-        </is>
-      </c>
-      <c r="F2" s="3">
-        <f>$D2 &amp; " " &amp; $E2</f>
-        <v/>
-      </c>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>cust0002</t>
+          <t>bob</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CUST0002</t>
+          <t>Bob</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>john.doe@email.com</t>
+          <t>bob@ssot.me</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>John</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Doe</t>
-        </is>
-      </c>
-      <c r="F3" s="3">
-        <f>$D3 &amp; " " &amp; $E3</f>
-        <v/>
-      </c>
+          <t>Mathemetician</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>widget1, widget2</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>cust0003</t>
+          <t>andy</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CUST0003</t>
+          <t>Andy</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>emily.jones@email.com</t>
+          <t>guest@ssot.me</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Emily</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Jones</t>
-        </is>
-      </c>
-      <c r="F4" s="3">
-        <f>$D4 &amp; " " &amp; $E4</f>
-        <v/>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>widget3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>bob2</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Bob2</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>bob@ssot.me</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ShapeId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sides</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>HowManySides</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>IsRectangle</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>IsTriangle</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>IsRightTriangle</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>SumOfInternalAngles</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>MaxAngle</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>HypotenuseLengthSquared</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>NonHypotenuseSidesSquared</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>PythagoreanTheoremHolds</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>shape1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Shape1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>shape1-side-a, shape1-side-b, shape1-side-c</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" s="3">
+        <f>AND($D2=4)</f>
+        <v/>
+      </c>
+      <c r="F2" s="3">
+        <f>AND($H2=180, $D2=3)</f>
+        <v/>
+      </c>
+      <c r="G2" s="3">
+        <f>AND($F2, $I2 = 90)</f>
+        <v/>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="L2" s="3">
+        <f>AND(
+  $G2,  
+  $J2 = $K2
+)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>shape2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Shape2</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>shape2-side-a, shape2-side-b, shape2-side-c, shape2-side-d</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" s="3">
+        <f>AND($D3=4)</f>
+        <v/>
+      </c>
+      <c r="F3" s="3">
+        <f>AND($H3=180, $D3=3)</f>
+        <v/>
+      </c>
+      <c r="G3" s="3">
+        <f>AND($F3, $I3 = 90)</f>
+        <v/>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="3">
+        <f>AND(
+  $G3,  
+  $J3 = $K3
+)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SideId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ShapeSides</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>IsRectangle</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>IsTriangle</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>IsRightTriangle</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>IsHypotenuse</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>StatusOfTheorem</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>PythagoreanTheoremHolds</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LengthSquared</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>HypotenuseLengthSquared</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>NonHypotenuseLengthSquared</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>PreviousSideLength</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>NextLength</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>PreviousAngle</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Angle</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>NextAngle</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>PreviousSide</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>NextSide</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Shape</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>PreviousLabel</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>NextLabel</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>shape1-side-a</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>$V2 &amp; "-Side-" &amp; $D2</f>
+        <v/>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H2" s="3">
+        <f>AND(
+  $F2,
+  $O2 &gt; $N2,
+  $O2 &gt; $P2
+)</f>
+        <v/>
+      </c>
+      <c r="I2" s="3">
+        <f>IF($F2, 
+  IF(AND($G2, NOT($J2)), 
+    "PYTHAGOREAN THEOREM FALSIFIED!", 
+    "Pythagorean Theorem Holds (obviously)."
+  ),
+  "NA"
+)</f>
+        <v/>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K2" s="3">
+        <f>$O2 * $O2</f>
+        <v/>
+      </c>
+      <c r="L2" s="3">
+        <f>IF($H2, $K2)</f>
+        <v/>
+      </c>
+      <c r="M2" s="3">
+        <f>IF(AND(NOT($H2), $F2), $K2)</f>
+        <v/>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>shape1-side-c</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>shape1-side-b</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>shape1</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>shape1-side-b</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>$V3 &amp; "-Side-" &amp; $D3</f>
+        <v/>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H3" s="3">
+        <f>AND(
+  $F3,
+  $O3 &gt; $N3,
+  $O3 &gt; $P3
+)</f>
+        <v/>
+      </c>
+      <c r="I3" s="3">
+        <f>IF($F3, 
+  IF(AND($G3, NOT($J3)), 
+    "PYTHAGOREAN THEOREM FALSIFIED!", 
+    "Pythagorean Theorem Holds (obviously)."
+  ),
+  "NA"
+)</f>
+        <v/>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K3" s="3">
+        <f>$O3 * $O3</f>
+        <v/>
+      </c>
+      <c r="L3" s="3">
+        <f>IF($H3, $K3)</f>
+        <v/>
+      </c>
+      <c r="M3" s="3">
+        <f>IF(AND(NOT($H3), $F3), $K3)</f>
+        <v/>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>shape1-side-a</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>shape1-side-c</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>shape1</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>shape1-side-c</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>$V4 &amp; "-Side-" &amp; $D4</f>
+        <v/>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H4" s="3">
+        <f>AND(
+  $F4,
+  $O4 &gt; $N4,
+  $O4 &gt; $P4
+)</f>
+        <v/>
+      </c>
+      <c r="I4" s="3">
+        <f>IF($F4, 
+  IF(AND($G4, NOT($J4)), 
+    "PYTHAGOREAN THEOREM FALSIFIED!", 
+    "Pythagorean Theorem Holds (obviously)."
+  ),
+  "NA"
+)</f>
+        <v/>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K4" s="3">
+        <f>$O4 * $O4</f>
+        <v/>
+      </c>
+      <c r="L4" s="3">
+        <f>IF($H4, $K4)</f>
+        <v/>
+      </c>
+      <c r="M4" s="3">
+        <f>IF(AND(NOT($H4), $F4), $K4)</f>
+        <v/>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>shape1-side-b</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>shape1-side-a</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>shape1</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>shape2-side-a</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>$V5 &amp; "-Side-" &amp; $D5</f>
+        <v/>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <f>AND(
+  $F5,
+  $O5 &gt; $N5,
+  $O5 &gt; $P5
+)</f>
+        <v/>
+      </c>
+      <c r="I5" s="3">
+        <f>IF($F5, 
+  IF(AND($G5, NOT($J5)), 
+    "PYTHAGOREAN THEOREM FALSIFIED!", 
+    "Pythagorean Theorem Holds (obviously)."
+  ),
+  "NA"
+)</f>
+        <v/>
+      </c>
+      <c r="J5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3">
+        <f>$O5 * $O5</f>
+        <v/>
+      </c>
+      <c r="L5" s="3">
+        <f>IF($H5, $K5)</f>
+        <v/>
+      </c>
+      <c r="M5" s="3">
+        <f>IF(AND(NOT($H5), $F5), $K5)</f>
+        <v/>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>shape2-side-d</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>shape2-side-b</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>shape2</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>shape2-side-b</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>$V6 &amp; "-Side-" &amp; $D6</f>
+        <v/>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <f>AND(
+  $F6,
+  $O6 &gt; $N6,
+  $O6 &gt; $P6
+)</f>
+        <v/>
+      </c>
+      <c r="I6" s="3">
+        <f>IF($F6, 
+  IF(AND($G6, NOT($J6)), 
+    "PYTHAGOREAN THEOREM FALSIFIED!", 
+    "Pythagorean Theorem Holds (obviously)."
+  ),
+  "NA"
+)</f>
+        <v/>
+      </c>
+      <c r="J6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3">
+        <f>$O6 * $O6</f>
+        <v/>
+      </c>
+      <c r="L6" s="3">
+        <f>IF($H6, $K6)</f>
+        <v/>
+      </c>
+      <c r="M6" s="3">
+        <f>IF(AND(NOT($H6), $F6), $K6)</f>
+        <v/>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>shape2-side-a</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>shape2-side-c</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>shape2</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>shape2-side-c</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>$V7 &amp; "-Side-" &amp; $D7</f>
+        <v/>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
+        <f>AND(
+  $F7,
+  $O7 &gt; $N7,
+  $O7 &gt; $P7
+)</f>
+        <v/>
+      </c>
+      <c r="I7" s="3">
+        <f>IF($F7, 
+  IF(AND($G7, NOT($J7)), 
+    "PYTHAGOREAN THEOREM FALSIFIED!", 
+    "Pythagorean Theorem Holds (obviously)."
+  ),
+  "NA"
+)</f>
+        <v/>
+      </c>
+      <c r="J7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3">
+        <f>$O7 * $O7</f>
+        <v/>
+      </c>
+      <c r="L7" s="3">
+        <f>IF($H7, $K7)</f>
+        <v/>
+      </c>
+      <c r="M7" s="3">
+        <f>IF(AND(NOT($H7), $F7), $K7)</f>
+        <v/>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>shape2-side-b</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>shape2-side-d</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>shape2</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>shape2-side-d</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>$V8 &amp; "-Side-" &amp; $D8</f>
+        <v/>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <f>AND(
+  $F8,
+  $O8 &gt; $N8,
+  $O8 &gt; $P8
+)</f>
+        <v/>
+      </c>
+      <c r="I8" s="3">
+        <f>IF($F8, 
+  IF(AND($G8, NOT($J8)), 
+    "PYTHAGOREAN THEOREM FALSIFIED!", 
+    "Pythagorean Theorem Holds (obviously)."
+  ),
+  "NA"
+)</f>
+        <v/>
+      </c>
+      <c r="J8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
+        <f>$O8 * $O8</f>
+        <v/>
+      </c>
+      <c r="L8" s="3">
+        <f>IF($H8, $K8)</f>
+        <v/>
+      </c>
+      <c r="M8" s="3">
+        <f>IF(AND(NOT($H8), $F8), $K8)</f>
+        <v/>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>shape2-side-c</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>shape2-side-a</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>shape2</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>WidgetId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Appuser</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Name_from_Appuser</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>EmailAddress_from_Appuser</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Role_from_Appuser</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>widget1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>widget1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>bob</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>bob@ssot.me</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Mathemetician</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>widget2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>widget2</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>bob</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>bob@ssot.me</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Mathemetician</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>pink</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>widget3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>widget3</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>andy</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>guest@ssot.me</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ERBVersionId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>BaseId</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Message</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>CommitDate</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>IsPublished</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>b0e261e6-9ded-4ed0-817a-12a82a538201-version-2026-02-06-22-18-34</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>$C2 &amp; "-" &amp; $D2</f>
+        <v/>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>b0e261e6-9ded-4ed0-817a-12a82a538201</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Version 2026-02-06 22:18:34</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>fixed custom RLS policies.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>b0e261e6-9ded-4ed0-817a-12a82a538201-version-2026-02-07-01-50-20</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>$C3 &amp; "-" &amp; $D3</f>
+        <v/>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>b0e261e6-9ded-4ed0-817a-12a82a538201</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Version 2026-02-07 01:50:20</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Trying to get data in as well.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>b0e261e6-9ded-4ed0-817a-12a82a538201-version-2026-02-07-01-54-24</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>$C4 &amp; "-" &amp; $D4</f>
+        <v/>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>b0e261e6-9ded-4ed0-817a-12a82a538201</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Version 2026-02-07 01:54:24</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Updated base again.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>e7b6e278-92b8-4a76-a3bf-d2b1183d1c77-version-2026-02-07-02-00-40</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>$C5 &amp; "-" &amp; $D5</f>
+        <v/>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>e7b6e278-92b8-4a76-a3bf-d2b1183d1c77</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Version 2026-02-07 02:00:40</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Trying to get data in the db.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>e7b6e278-92b8-4a76-a3bf-d2b1183d1c77-version-2026-02-07-02-18-06</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>$C6 &amp; "-" &amp; $D6</f>
+        <v/>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>e7b6e278-92b8-4a76-a3bf-d2b1183d1c77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Version 2026-02-07 02:18:06</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Added app users.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>e7b6e278-92b8-4a76-a3bf-d2b1183d1c77-version-2026-02-07-02-27-57</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>$C7 &amp; "-" &amp; $D7</f>
+        <v/>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>e7b6e278-92b8-4a76-a3bf-d2b1183d1c77</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Version 2026-02-07 02:27:57</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Added AppUsers.IsActive</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>e7b6e278-92b8-4a76-a3bf-d2b1183d1c77-version-2026-02-07-22-46-12</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>$C8 &amp; "-" &amp; $D8</f>
+        <v/>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>e7b6e278-92b8-4a76-a3bf-d2b1183d1c77</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Version 2026-02-07 22:46:12</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>trying new admin/anon users.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>e7b6e278-92b8-4a76-a3bf-d2b1183d1c77-version-2026-02-07-22-47-11</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>$C9 &amp; "-" &amp; $D9</f>
+        <v/>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>e7b6e278-92b8-4a76-a3bf-d2b1183d1c77</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Version 2026-02-07 22:47:11</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>added admin/anon users.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>f4cefffd-29c7-4dc6-8b5b-2142c62a475c-version-2026-02-08-03-55-18</t>
+        </is>
+      </c>
+      <c r="B10" s="3">
+        <f>$C10 &amp; "-" &amp; $D10</f>
+        <v/>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>f4cefffd-29c7-4dc6-8b5b-2142c62a475c</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Version 2026-02-08 03:55:18</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>fixing auth</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>f4cefffd-29c7-4dc6-8b5b-2142c62a475c-version-2026-02-09-06-07-44</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>$C11 &amp; "-" &amp; $D11</f>
+        <v/>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>f4cefffd-29c7-4dc6-8b5b-2142c62a475c</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Version 2026-02-09 06:07:44</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>temp 4</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>f4cefffd-29c7-4dc6-8b5b-2142c62a475c-version-2026-02-09-06-14-38</t>
+        </is>
+      </c>
+      <c r="B12" s="3">
+        <f>$C12 &amp; "-" &amp; $D12</f>
+        <v/>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>f4cefffd-29c7-4dc6-8b5b-2142c62a475c</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Version 2026-02-09 06:14:38</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>added ownership records to widgets</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>f4cefffd-29c7-4dc6-8b5b-2142c62a475c-version-2026-02-09-07-22-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>$C13 &amp; "-" &amp; $D13</f>
+        <v/>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>f4cefffd-29c7-4dc6-8b5b-2142c62a475c</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Version 2026-02-09 07:22:15</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>test preserving builders</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>f4cefffd-29c7-4dc6-8b5b-2142c62a475c-version-2026-02-09-07-41-26</t>
+        </is>
+      </c>
+      <c r="B14" s="3">
+        <f>$C14 &amp; "-" &amp; $D14</f>
+        <v/>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>f4cefffd-29c7-4dc6-8b5b-2142c62a475c</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Version 2026-02-09 07:41:26</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>preserves policies now?</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>f4cefffd-29c7-4dc6-8b5b-2142c62a475c-version-2026-02-09-07-46-04</t>
+        </is>
+      </c>
+      <c r="B15" s="3">
+        <f>$C15 &amp; "-" &amp; $D15</f>
+        <v/>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>f4cefffd-29c7-4dc6-8b5b-2142c62a475c</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Version 2026-02-09 07:46:04</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>added color to widgets</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>f4cefffd-29c7-4dc6-8b5b-2142c62a475c-version-2026-02-11-00-40-18</t>
+        </is>
+      </c>
+      <c r="B16" s="3">
+        <f>$C16 &amp; "-" &amp; $D16</f>
+        <v/>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>f4cefffd-29c7-4dc6-8b5b-2142c62a475c</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Version 2026-02-11 00:40:18</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>added another b ob.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ERBCustomizationId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>SQLCode</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>SQLTarget</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>CustomizationType</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>03a-customize-schema-sql</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>03a-customize-schema.sql</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Customize Schema</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-- ============================================================================
+-- CUSTOMIZE SCHEMA - User-defined tables and schema modifications
+-- ============================================================================
+-- This file is for YOUR custom schema changes that should persist across
+-- regeneration of the base ERB files.
+--
+-- USE THIS FILE FOR:
+--   - Additional tables not defined in the rulebook
+--   - Extra columns on existing tables (ALTER TABLE)
+--   - Custom indexes for performance tuning
+--   - Custom constraints or triggers
+--
+-- IMPORTANT:
+--   - This file runs AFTER 01-drop-and-create-tables.sql
+--   - The base tables already exist when this runs
+--   - This file will NOT be overwritten by ERB regeneration
+--
+-- ============================================================================
+-- Your custom schema changes go here:
+</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Postgres</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>03b-customize-functions-sql</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>03b-customize-functions.sql</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Customize Functions</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-- ============================================================================
+-- CUSTOMIZE FUNCTIONS - User-defined calculation functions
+-- ============================================================================
+-- This file is for YOUR custom PostgreSQL functions that should persist
+-- across regeneration of the base ERB files.
+--
+-- IMPORTANT:
+--   - This file runs AFTER 02-create-functions.sql
+--   - Base ERB calc functions already exist when this runs
+--   - This file will NOT be overwritten by ERB regeneration
+--
+-- ============================================================================
+-- Your custom functions go here:
+CREATE OR REPLACE FUNCTION public.calc_shapes_hypotenuse_length_squared(p_shape_id text)
+ RETURNS numeric
+ LANGUAGE plpgsql
+ STABLE SECURITY DEFINER
+AS $function$
+BEGIN
+  RETURN ((SELECT COALESCE(MAX(calc_sides_hypotenuse_length_squared(side_id)), 0) FROM sides WHERE shape = p_shape_id));
+END;
+$function$;
+CREATE OR REPLACE FUNCTION public.calc_sides_length_squared(p_side_id text)
+ RETURNS integer
+ LANGUAGE plpgsql
+ STABLE SECURITY DEFINER
+AS $function$
+BEGIN
+  RETURN ((SELECT length FROM sides WHERE side_id = p_side_id) * (SELECT length FROM sides WHERE side_id = p_side_id));
+END;
+$function$;
+CREATE OR REPLACE FUNCTION public.calc_shapes_hypotenuse_length_squared(p_shape_id text)
+ RETURNS numeric
+ LANGUAGE plpgsql
+ STABLE SECURITY DEFINER
+AS $function$
+BEGIN
+  RETURN ((SELECT COALESCE(MAX(calc_sides_hypotenuse_length_squared(side_id)), 0) FROM sides WHERE shape = p_shape_id));
+END;
+$function$;
+</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Postgres</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Functions</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>03c-customize-views-sql</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>03c-customize-views.sql</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Customize Views</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-- ============================================================================
+-- CUSTOMIZE VIEWS - User-defined views and view extensions
+-- ============================================================================
+-- This file is for YOUR custom views that should persist across
+-- regeneration of the base ERB files.
+--
+-- IMPORTANT:
+--   - This file runs AFTER 03-create-views.sql
+--   - All base vw_* views already exist when this runs
+--   - This file will NOT be overwritten by ERB regeneration
+--
+-- ============================================================================
+-- Your custom views go here:
+</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Postgres</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Views</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>03d-customize-rls-sql</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>03d-customize-rls.sql</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Customize Policies (RLS)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-- ============================================================================
+-- CUSTOMIZE POLICIES - User-defined Row Level Security policies
+-- ============================================================================
+-- This file is for YOUR custom RLS policies that should persist across
+-- regeneration of the base ERB files.
+--
+-- IMPORTANT:
+--   - This file runs AFTER 04-create-policies.sql
+--   - Base RLS policies already exist when this runs
+--   - This file will NOT be overwritten by ERB regeneration
+--
+-- ============================================================================
+-- Your custom policies go here:
+</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Postgres</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>RLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>03e-customize-data-sql</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>03e-customize-data.sql</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Customize Data (Seeds / Migrations)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-- ============================================================================
+-- CUSTOMIZE DATA - User-defined seed data and data migrations
+-- ============================================================================
+-- This file is for YOUR custom seed data that should persist across
+-- regeneration of the base ERB files.
+--
+-- IMPORTANT:
+--   - This file runs AFTER 05-insert-data.sql
+--   - Base seed data already exists when this runs
+--   - This file will NOT be overwritten by ERB regeneration
+--
+-- ============================================================================
+-- Your custom data inserts go here:
+</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Postgres</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MagicLinkIntegrationId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>TenantId</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>PublicKeyPem</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>UserTableName</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>EmailField</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>RoleField</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>IsActiveField</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>UserIdField</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>AllowedAlgorithms</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>RequireTenantBinding</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>UseEmailDagPattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>magic-link-config</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Magic Link Config</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>c03e9d56-9525-47dd-9ee1-2f2a20383048</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>-----BEGIN PUBLIC KEY-----
+MIIBIjANBgkqhkiG9w0BAQEFAAOCAQ8AMIIBCgKCAQEA2XyDcVliu0wjQjDY1Rez
+/krdzYL3v4TXCJbYu2V1EkrKlVjO+ZGCIHu0yMAw5A+cUMm5cXtYyIXNln6tCg0M
+LHcNVrSDm5QuQSUuGP/SVrgSUItyrGfLZOwl+kYXgMmle4t11ecVhkaVARisBcRz
+Irh9ofSNtLR6UlJzKH4uFFswId5HrgwMCbart2YcrA7lrEt1hqASZ7pPPX6/i771
+97VqSf+clLX3Wq5VwyrtC9taTiVZrN/OhtWbSAkUX+NMkCc57MN4CcjP3/8JXbjv
+4L5ExZOpc14zRhOnOnC0cHRX475WoJbjI3+EfYDjaNrV6MVd444S/8HOOz3D8Pki
+XwIDAQAB
+-----END PUBLIC KEY-----</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>app_users</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>email_address</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>is_active</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>RS256</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/execution-substrates/xlsx/rulebook.xlsx
+++ b/execution-substrates/xlsx/rulebook.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Customers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -536,7 +536,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Mary</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="F2" s="3">
-        <f>$E2 &amp; ", " &amp; $D2</f>
+        <f>$D2 &amp; " " &amp; $E2</f>
         <v/>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Jimmy</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="F3" s="3">
-        <f>$E3 &amp; ", " &amp; $D3</f>
+        <f>$D3 &amp; " " &amp; $E3</f>
         <v/>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Mary</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="F4" s="3">
-        <f>$E4 &amp; ", " &amp; $D4</f>
+        <f>$D4 &amp; " " &amp; $E4</f>
         <v/>
       </c>
     </row>

--- a/execution-substrates/xlsx/rulebook.xlsx
+++ b/execution-substrates/xlsx/rulebook.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -521,13 +521,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>cust0001</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>CUST0001</t>
-        </is>
+          <t>jane-smith-email-com</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>SUBSTITUTE($C2, "@", "-")</f>
+        <v/>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -536,7 +535,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Bob</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -552,13 +551,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>cust0002</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>CUST0002</t>
-        </is>
+          <t>john-doe-email-com</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>SUBSTITUTE($C3, "@", "-")</f>
+        <v/>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -583,13 +581,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>cust0003</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>CUST0003</t>
-        </is>
+          <t>emily-jones-email-com</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>SUBSTITUTE($C4, "@", "-")</f>
+        <v/>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>

--- a/execution-substrates/xlsx/rulebook.xlsx
+++ b/execution-substrates/xlsx/rulebook.xlsx
@@ -7,7 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projects" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Employees" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roles" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TypesOfProject" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +493,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CustomerId</t>
+          <t>ClientId</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -531,12 +535,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>jane.smith@email.com</t>
+          <t>larry.smith@email.com</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Bob</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -567,7 +571,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Jimmy</t>
+          <t>John</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -598,7 +602,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Mary</t>
+          <t>Emily</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -615,4 +619,805 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ProjectId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ProjectType</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ProjectTypeName</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ProjectTypeDescription</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ProjectTypeRequiresManagerApproval</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>DueDate</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>IsApproved</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ApprovedBy</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ApprovedByRoleIsManager</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ApprovedByName</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ApprovedByEmailAddress</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ApprovedByPhoneNumber</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>internal-tools-dashboard</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Internal Tools Dashboard</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Build internal analytics dashboard for team productivity metrics</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>An internal project that is not publicly accessible</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>sarah-chen</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Sarah Chen</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>sarah.chen@acmecorp.example</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>555-0101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>customer-portal-redesign</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Customer Portal Redesign</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Complete redesign of customer-facing portal with modern UX</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>clientfacing</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>ClientFacing</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Open, public facing communication</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>priya-patel</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Priya Patel</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>priya.patel@acmecorp.example</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>555-0103</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>gdpr-compliance-audit</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>GDPR Compliance Audit</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Annual compliance audit and documentation update</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>compliance</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>mike-johnson</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Mike Johnson</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>mike.johnson@acmecorp.example</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>555-0102</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>EmailAddress</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>PhoneNumber</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>RoleName</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>RoleDescription</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Projects</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>RoleIsManager</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>sarah-chen</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Sarah Chen</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>sarah.chen@acmecorp.example</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>555-0101</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>projectmanager</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>ProjectManager</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>The project Manager makes sure that the developers do what the analysts ask for</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>internal-tools-dashboard</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>mike-johnson</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Mike Johnson</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>mike.johnson@acmecorp.example</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>555-0102</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Developers handle the implementation and are responsible for making the final product do what is expected</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>gdpr-compliance-audit</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>priya-patel</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Priya Patel</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>priya.patel@acmecorp.example</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>555-0103</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>The business analysis know what the customer's want.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>customer-portal-redesign</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>RoleId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>IsManager</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Employees</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>CountOfEmployees</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Developers handle the implementation and are responsible for making the final product do what is expected</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>mike-johnson</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>projectmanager</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ProjectManager</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>The project Manager makes sure that the developers do what the analysts ask for</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>sarah-chen</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>The business analysis know what the customer's want.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>priya-patel</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TypesOfProjectId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>RequiresManagerApproval</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Projects</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>CountOfProjects</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>An internal project that is not publicly accessible</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>internal-tools-dashboard</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>clientfacing</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ClientFacing</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Open, public facing communication</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>customer-portal-redesign</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>compliance</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>gdpr-compliance-audit</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/execution-substrates/xlsx/rulebook.xlsx
+++ b/execution-substrates/xlsx/rulebook.xlsx
@@ -7,11 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projects" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Employees" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roles" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TypesOfProject" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERBVersions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERBCustomizations" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -493,12 +491,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ClientId</t>
+          <t>CustomerId</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -525,22 +523,21 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>cust0001</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>CUST0001</t>
-        </is>
+          <t>jane-smith-email-com</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>SUBSTITUTE($C2, "@", "-")</f>
+        <v/>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>larry.smith@email.com</t>
+          <t>jane.smith@email.com</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Bob</t>
+          <t>Bobby</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -549,20 +546,19 @@
         </is>
       </c>
       <c r="F2" s="3">
-        <f>$D2 &amp; " " &amp; $E2</f>
+        <f>$E2 &amp; ", " &amp; $D2</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>cust0002</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>CUST0002</t>
-        </is>
+          <t>john-doe-email-com</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>SUBSTITUTE($C3, "@", "-")</f>
+        <v/>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -571,7 +567,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Jimmy</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -580,20 +576,19 @@
         </is>
       </c>
       <c r="F3" s="3">
-        <f>$D3 &amp; " " &amp; $E3</f>
+        <f>$E3 &amp; ", " &amp; $D3</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>cust0003</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>CUST0003</t>
-        </is>
+          <t>emily-jones-email-com</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>SUBSTITUTE($C4, "@", "-")</f>
+        <v/>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -602,7 +597,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Mary</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -611,7 +606,7 @@
         </is>
       </c>
       <c r="F4" s="3">
-        <f>$D4 &amp; " " &amp; $E4</f>
+        <f>$E4 &amp; ", " &amp; $D4</f>
         <v/>
       </c>
     </row>
@@ -627,292 +622,52 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ProjectId</t>
+          <t>ERBVersionId</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>BaseId</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>ProjectType</t>
+          <t>Message</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ProjectTypeName</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ProjectTypeDescription</t>
+          <t>CommitDate</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ProjectTypeRequiresManagerApproval</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>DueDate</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>IsApproved</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ApprovedBy</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>ApprovedByRoleIsManager</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>ApprovedByName</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>ApprovedByEmailAddress</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>ApprovedByPhoneNumber</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>internal-tools-dashboard</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Internal Tools Dashboard</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Build internal analytics dashboard for team productivity metrics</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>internal</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>An internal project that is not publicly accessible</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>sarah-chen</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Sarah Chen</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>sarah.chen@acmecorp.example</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>555-0101</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>customer-portal-redesign</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Customer Portal Redesign</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Complete redesign of customer-facing portal with modern UX</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>clientfacing</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>ClientFacing</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Open, public facing communication</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>priya-patel</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>Priya Patel</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>priya.patel@acmecorp.example</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>555-0103</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>gdpr-compliance-audit</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>GDPR Compliance Audit</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Annual compliance audit and documentation update</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>compliance</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>mike-johnson</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Mike Johnson</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>mike.johnson@acmecorp.example</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>555-0102</t>
+          <t>IsPublished</t>
         </is>
       </c>
     </row>
@@ -927,24 +682,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>EmployeeId</t>
+          <t>ERBCustomizationId</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -954,467 +706,254 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>EmailAddress</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>PhoneNumber</t>
+          <t>SQLCode</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>SQLTarget</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>RoleName</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>RoleDescription</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Projects</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>RoleIsManager</t>
+          <t>CustomizationType</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>sarah-chen</t>
+          <t>03a-customize-schema-sql</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Sarah Chen</t>
+          <t>03a-customize-schema.sql</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>sarah.chen@acmecorp.example</t>
+          <t>Customize Schema</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>555-0101</t>
+          <t xml:space="preserve">-- ============================================================================
+-- CUSTOMIZE SCHEMA - User-defined tables and schema modifications
+-- ============================================================================
+-- This file is for YOUR custom schema changes that should persist across
+-- regeneration of the base ERB files.
+--
+-- USE THIS FILE FOR:
+--   - Additional tables not defined in the rulebook
+--   - Extra columns on existing tables (ALTER TABLE)
+--   - Custom indexes for performance tuning
+--   - Custom constraints or triggers
+--
+-- IMPORTANT:
+--   - This file runs AFTER 01-drop-and-create-tables.sql
+--   - The base tables already exist when this runs
+--   - This file will NOT be overwritten by ERB regeneration
+--
+-- ============================================================================
+-- Your custom schema changes go here:
+</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>projectmanager</t>
+          <t>Postgres</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>ProjectManager</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>The project Manager makes sure that the developers do what the analysts ask for</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>internal-tools-dashboard</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
+          <t>Schema</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>mike-johnson</t>
+          <t>03b-customize-functions-sql</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Mike Johnson</t>
+          <t>03b-customize-functions.sql</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>mike.johnson@acmecorp.example</t>
+          <t>Customize Functions</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>555-0102</t>
+          <t xml:space="preserve">-- ============================================================================
+-- CUSTOMIZE FUNCTIONS - User-defined calculation functions
+-- ============================================================================
+-- This file is for YOUR custom PostgreSQL functions that should persist
+-- across regeneration of the base ERB files.
+--
+-- IMPORTANT:
+--   - This file runs AFTER 02-create-functions.sql
+--   - Base ERB calc functions already exist when this runs
+--   - This file will NOT be overwritten by ERB regeneration
+--
+-- ============================================================================
+-- Your custom functions go here:
+</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>developer</t>
+          <t>Postgres</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Developer</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Developers handle the implementation and are responsible for making the final product do what is expected</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>gdpr-compliance-audit</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
+          <t>Functions</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>priya-patel</t>
+          <t>03c-customize-views-sql</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Priya Patel</t>
+          <t>03c-customize-views.sql</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>priya.patel@acmecorp.example</t>
+          <t>Customize Views</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>555-0103</t>
+          <t xml:space="preserve">-- ============================================================================
+-- CUSTOMIZE VIEWS - User-defined views and view extensions
+-- ============================================================================
+-- This file is for YOUR custom views that should persist across
+-- regeneration of the base ERB files.
+--
+-- IMPORTANT:
+--   - This file runs AFTER 03-create-views.sql
+--   - All base vw_* views already exist when this runs
+--   - This file will NOT be overwritten by ERB regeneration
+--
+-- ============================================================================
+-- Your custom views go here:
+</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>analyst</t>
+          <t>Postgres</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>The business analysis know what the customer's want.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>customer-portal-redesign</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>RoleId</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>IsManager</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Employees</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>CountOfEmployees</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>developer</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Developer</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Developers handle the implementation and are responsible for making the final product do what is expected</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>mike-johnson</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>projectmanager</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>ProjectManager</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>The project Manager makes sure that the developers do what the analysts ask for</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>sarah-chen</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>The business analysis know what the customer's want.</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>priya-patel</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>TypesOfProjectId</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>RequiresManagerApproval</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Projects</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>CountOfProjects</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>internal</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>An internal project that is not publicly accessible</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>internal-tools-dashboard</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>clientfacing</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>ClientFacing</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Open, public facing communication</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>customer-portal-redesign</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="n">
-        <v>0</v>
+          <t>Views</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>compliance</t>
+          <t>03d-customize-rls-sql</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="b">
-        <v>1</v>
+          <t>03d-customize-rls.sql</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Customize Policies (RLS)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-- ============================================================================
+-- CUSTOMIZE POLICIES - User-defined Row Level Security policies
+-- ============================================================================
+-- This file is for YOUR custom RLS policies that should persist across
+-- regeneration of the base ERB files.
+--
+-- IMPORTANT:
+--   - This file runs AFTER 04-create-policies.sql
+--   - Base RLS policies already exist when this runs
+--   - This file will NOT be overwritten by ERB regeneration
+--
+-- ============================================================================
+-- Your custom policies go here:
+</t>
+        </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>gdpr-compliance-audit</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>1</v>
+          <t>Postgres</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>RLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>03e-customize-data-sql</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>03e-customize-data.sql</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Customize Data (Seeds / Migrations)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-- ============================================================================
+-- CUSTOMIZE DATA - User-defined seed data and data migrations
+-- ============================================================================
+-- This file is for YOUR custom seed data that should persist across
+-- regeneration of the base ERB files.
+--
+-- IMPORTANT:
+--   - This file runs AFTER 05-insert-data.sql
+--   - Base seed data already exists when this runs
+--   - This file will NOT be overwritten by ERB regeneration
+--
+-- ============================================================================
+-- Your custom data inserts go here:
+</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Postgres</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/execution-substrates/xlsx/rulebook.xlsx
+++ b/execution-substrates/xlsx/rulebook.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERBVersions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERBCustomizations" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -496,7 +494,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -523,12 +521,13 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>jane-smith-email-com</t>
-        </is>
-      </c>
-      <c r="B2" s="3">
-        <f>SUBSTITUTE($C2, "@", "-")</f>
-        <v/>
+          <t>cust0001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>CUST0001</t>
+        </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -537,7 +536,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Bobby</t>
+          <t>Jane</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -553,12 +552,13 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>john-doe-email-com</t>
-        </is>
-      </c>
-      <c r="B3" s="3">
-        <f>SUBSTITUTE($C3, "@", "-")</f>
-        <v/>
+          <t>cust0002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>CUST0002</t>
+        </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -567,7 +567,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Jimmy</t>
+          <t>John</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -583,12 +583,13 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>emily-jones-email-com</t>
-        </is>
-      </c>
-      <c r="B4" s="3">
-        <f>SUBSTITUTE($C4, "@", "-")</f>
-        <v/>
+          <t>cust0003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>CUST0003</t>
+        </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -597,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Mary</t>
+          <t>Emily</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -614,349 +615,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ERBVersionId</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>BaseId</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Message</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>CommitDate</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>IsPublished</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ERBCustomizationId</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>SQLCode</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>SQLTarget</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>CustomizationType</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>03a-customize-schema-sql</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>03a-customize-schema.sql</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Customize Schema</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-- ============================================================================
--- CUSTOMIZE SCHEMA - User-defined tables and schema modifications
--- ============================================================================
--- This file is for YOUR custom schema changes that should persist across
--- regeneration of the base ERB files.
---
--- USE THIS FILE FOR:
---   - Additional tables not defined in the rulebook
---   - Extra columns on existing tables (ALTER TABLE)
---   - Custom indexes for performance tuning
---   - Custom constraints or triggers
---
--- IMPORTANT:
---   - This file runs AFTER 01-drop-and-create-tables.sql
---   - The base tables already exist when this runs
---   - This file will NOT be overwritten by ERB regeneration
---
--- ============================================================================
--- Your custom schema changes go here:
-</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Postgres</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Schema</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>03b-customize-functions-sql</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>03b-customize-functions.sql</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Customize Functions</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-- ============================================================================
--- CUSTOMIZE FUNCTIONS - User-defined calculation functions
--- ============================================================================
--- This file is for YOUR custom PostgreSQL functions that should persist
--- across regeneration of the base ERB files.
---
--- IMPORTANT:
---   - This file runs AFTER 02-create-functions.sql
---   - Base ERB calc functions already exist when this runs
---   - This file will NOT be overwritten by ERB regeneration
---
--- ============================================================================
--- Your custom functions go here:
-</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Postgres</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Functions</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>03c-customize-views-sql</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>03c-customize-views.sql</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Customize Views</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-- ============================================================================
--- CUSTOMIZE VIEWS - User-defined views and view extensions
--- ============================================================================
--- This file is for YOUR custom views that should persist across
--- regeneration of the base ERB files.
---
--- IMPORTANT:
---   - This file runs AFTER 03-create-views.sql
---   - All base vw_* views already exist when this runs
---   - This file will NOT be overwritten by ERB regeneration
---
--- ============================================================================
--- Your custom views go here:
-</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Postgres</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Views</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>03d-customize-rls-sql</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>03d-customize-rls.sql</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Customize Policies (RLS)</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-- ============================================================================
--- CUSTOMIZE POLICIES - User-defined Row Level Security policies
--- ============================================================================
--- This file is for YOUR custom RLS policies that should persist across
--- regeneration of the base ERB files.
---
--- IMPORTANT:
---   - This file runs AFTER 04-create-policies.sql
---   - Base RLS policies already exist when this runs
---   - This file will NOT be overwritten by ERB regeneration
---
--- ============================================================================
--- Your custom policies go here:
-</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Postgres</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>RLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>03e-customize-data-sql</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>03e-customize-data.sql</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Customize Data (Seeds / Migrations)</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-- ============================================================================
--- CUSTOMIZE DATA - User-defined seed data and data migrations
--- ============================================================================
--- This file is for YOUR custom seed data that should persist across
--- regeneration of the base ERB files.
---
--- IMPORTANT:
---   - This file runs AFTER 05-insert-data.sql
---   - Base seed data already exists when this runs
---   - This file will NOT be overwritten by ERB regeneration
---
--- ============================================================================
--- Your custom data inserts go here:
-</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Postgres</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/execution-substrates/xlsx/rulebook.xlsx
+++ b/execution-substrates/xlsx/rulebook.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERBVersions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERBCustomizations" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -494,7 +496,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -521,13 +523,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>cust0001</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>CUST0001</t>
-        </is>
+          <t>jane-smith-email-com</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>SUBSTITUTE($C2, "@", "-")</f>
+        <v/>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -536,7 +537,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Bobby</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -552,13 +553,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>cust0002</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>CUST0002</t>
-        </is>
+          <t>john-doe-email-com</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>SUBSTITUTE($C3, "@", "-")</f>
+        <v/>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -567,7 +567,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Jimmy</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -583,13 +583,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>cust0003</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>CUST0003</t>
-        </is>
+          <t>emily-jones-email-com</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>SUBSTITUTE($C4, "@", "-")</f>
+        <v/>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -598,7 +597,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Mary</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -615,4 +614,349 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ERBVersionId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>BaseId</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Message</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>CommitDate</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>IsPublished</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ERBCustomizationId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>SQLCode</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>SQLTarget</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>CustomizationType</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>03a-customize-schema-sql</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>03a-customize-schema.sql</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Customize Schema</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-- ============================================================================
+-- CUSTOMIZE SCHEMA - User-defined tables and schema modifications
+-- ============================================================================
+-- This file is for YOUR custom schema changes that should persist across
+-- regeneration of the base ERB files.
+--
+-- USE THIS FILE FOR:
+--   - Additional tables not defined in the rulebook
+--   - Extra columns on existing tables (ALTER TABLE)
+--   - Custom indexes for performance tuning
+--   - Custom constraints or triggers
+--
+-- IMPORTANT:
+--   - This file runs AFTER 01-drop-and-create-tables.sql
+--   - The base tables already exist when this runs
+--   - This file will NOT be overwritten by ERB regeneration
+--
+-- ============================================================================
+-- Your custom schema changes go here:
+</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Postgres</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>03b-customize-functions-sql</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>03b-customize-functions.sql</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Customize Functions</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-- ============================================================================
+-- CUSTOMIZE FUNCTIONS - User-defined calculation functions
+-- ============================================================================
+-- This file is for YOUR custom PostgreSQL functions that should persist
+-- across regeneration of the base ERB files.
+--
+-- IMPORTANT:
+--   - This file runs AFTER 02-create-functions.sql
+--   - Base ERB calc functions already exist when this runs
+--   - This file will NOT be overwritten by ERB regeneration
+--
+-- ============================================================================
+-- Your custom functions go here:
+</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Postgres</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Functions</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>03c-customize-views-sql</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>03c-customize-views.sql</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Customize Views</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-- ============================================================================
+-- CUSTOMIZE VIEWS - User-defined views and view extensions
+-- ============================================================================
+-- This file is for YOUR custom views that should persist across
+-- regeneration of the base ERB files.
+--
+-- IMPORTANT:
+--   - This file runs AFTER 03-create-views.sql
+--   - All base vw_* views already exist when this runs
+--   - This file will NOT be overwritten by ERB regeneration
+--
+-- ============================================================================
+-- Your custom views go here:
+</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Postgres</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Views</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>03d-customize-rls-sql</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>03d-customize-rls.sql</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Customize Policies (RLS)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-- ============================================================================
+-- CUSTOMIZE POLICIES - User-defined Row Level Security policies
+-- ============================================================================
+-- This file is for YOUR custom RLS policies that should persist across
+-- regeneration of the base ERB files.
+--
+-- IMPORTANT:
+--   - This file runs AFTER 04-create-policies.sql
+--   - Base RLS policies already exist when this runs
+--   - This file will NOT be overwritten by ERB regeneration
+--
+-- ============================================================================
+-- Your custom policies go here:
+</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Postgres</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>RLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>03e-customize-data-sql</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>03e-customize-data.sql</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Customize Data (Seeds / Migrations)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-- ============================================================================
+-- CUSTOMIZE DATA - User-defined seed data and data migrations
+-- ============================================================================
+-- This file is for YOUR custom seed data that should persist across
+-- regeneration of the base ERB files.
+--
+-- IMPORTANT:
+--   - This file runs AFTER 05-insert-data.sql
+--   - Base seed data already exists when this runs
+--   - This file will NOT be overwritten by ERB regeneration
+--
+-- ============================================================================
+-- Your custom data inserts go here:
+</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Postgres</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/execution-substrates/xlsx/rulebook.xlsx
+++ b/execution-substrates/xlsx/rulebook.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -521,13 +521,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>cust0001</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>CUST0001</t>
-        </is>
+          <t>jane-smith-email-com</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>SUBSTITUTE($C2, "@", "-")</f>
+        <v/>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -536,7 +535,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Bobby</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -552,13 +551,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>cust0002</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>CUST0002</t>
-        </is>
+          <t>john-doe-email-com</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>SUBSTITUTE($C3, "@", "-")</f>
+        <v/>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -567,7 +565,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Jimmy</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -583,13 +581,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>cust0003</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>CUST0003</t>
-        </is>
+          <t>emily-jones-email-com</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>SUBSTITUTE($C4, "@", "-")</f>
+        <v/>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -598,7 +595,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Mary</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">

--- a/execution-substrates/xlsx/rulebook.xlsx
+++ b/execution-substrates/xlsx/rulebook.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Bobby</t>
+          <t>Jane</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="F2" s="3">
-        <f>$E2 &amp; ", " &amp; $D2</f>
+        <f>$D2 &amp; " " &amp; $E2</f>
         <v/>
       </c>
     </row>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="F3" s="3">
-        <f>$E3 &amp; ", " &amp; $D3</f>
+        <f>$D3 &amp; " " &amp; $E3</f>
         <v/>
       </c>
     </row>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="F4" s="3">
-        <f>$E4 &amp; ", " &amp; $D4</f>
+        <f>$D4 &amp; " " &amp; $E4</f>
         <v/>
       </c>
     </row>

--- a/execution-substrates/xlsx/rulebook.xlsx
+++ b/execution-substrates/xlsx/rulebook.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="__meta__" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -160,22 +159,27 @@
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>First Name of the customer</t>
+        <t>Identifier for the customer.</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Last Name of the customer</t>
+        <t>The customer's email address</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>Full name: first and last</t>
+        <t>First Name of the customer - used to make the full name</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>First letter of the first and last name</t>
+        <t>Last Name of the customer - used to make the full name</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Full name is computed from the first and last name of the customer</t>
       </text>
     </comment>
   </commentList>
@@ -471,14 +475,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -489,122 +494,117 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>EmailAddress</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>FirstName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>LastName</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Initials</t>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>FullName</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>jane-smith</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Jane</t>
-        </is>
+          <t>bob-gmail-com</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>SUBSTITUTE($C2, "@", "-")</f>
+        <v/>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>bob@gmail.com</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Bobby</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>Smith</t>
         </is>
       </c>
-      <c r="D2" s="3">
-        <f>$C2 &amp; ", " &amp; $B2</f>
-        <v/>
-      </c>
-      <c r="E2" s="3">
-        <f>LEFT($B2, 1) &amp;LEFT($C2, 1)</f>
+      <c r="F2" s="3">
+        <f>$D2 &amp; " " &amp; $E2</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>john-doe</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>John</t>
-        </is>
+          <t>jimmy-gmail-com</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>SUBSTITUTE($C3, "@", "-")</f>
+        <v/>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>jimmy@gmail.com</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Jimmy</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>Doe</t>
         </is>
       </c>
-      <c r="D3" s="3">
-        <f>$C3 &amp; ", " &amp; $B3</f>
-        <v/>
-      </c>
-      <c r="E3" s="3">
-        <f>LEFT($B3, 1) &amp;LEFT($C3, 1)</f>
+      <c r="F3" s="3">
+        <f>$D3 &amp; " " &amp; $E3</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>emily-jones</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Emily</t>
-        </is>
+          <t>mary-gmail-com</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>SUBSTITUTE($C4, "@", "-")</f>
+        <v/>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>mary@gmail.com</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Mary</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>Jones</t>
         </is>
       </c>
-      <c r="D4" s="3">
-        <f>$C4 &amp; ", " &amp; $B4</f>
-        <v/>
-      </c>
-      <c r="E4" s="3">
-        <f>LEFT($B4, 1) &amp;LEFT($C4, 1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>mary-gutknecht</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Mary</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Gutknecht</t>
-        </is>
-      </c>
-      <c r="D5" s="3">
-        <f>$C5 &amp; ", " &amp; $B5</f>
-        <v/>
-      </c>
-      <c r="E5" s="3">
-        <f>LEFT($B5, 1) &amp;LEFT($C5, 1)</f>
+      <c r="F4" s="3">
+        <f>$D4 &amp; " " &amp; $E4</f>
         <v/>
       </c>
     </row>
@@ -612,52 +612,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>MetaKey</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ValueType</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>StringValue</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>JsonValue</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>